--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265704</v>
+        <v>123265699</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873421</v>
+        <v>873321</v>
       </c>
       <c r="R2" t="n">
-        <v>7392291</v>
+        <v>7392268</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123265707</v>
+        <v>123269165</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,35 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873355</v>
+        <v>873352</v>
       </c>
       <c r="R3" t="n">
         <v>7392213</v>
@@ -861,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265698</v>
+        <v>123269178</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +895,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873363</v>
+        <v>873536</v>
       </c>
       <c r="R4" t="n">
-        <v>7392320</v>
+        <v>7392501</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -963,28 +970,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265694</v>
+        <v>123269166</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +1001,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873473</v>
+        <v>873390</v>
       </c>
       <c r="R5" t="n">
-        <v>7392448</v>
+        <v>7392303</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1059,36 +1070,32 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265711</v>
+        <v>123269175</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1122,16 +1129,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873476</v>
+        <v>873408</v>
       </c>
       <c r="R6" t="n">
-        <v>7392450</v>
+        <v>7392282</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1172,28 +1182,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265692</v>
+        <v>123265709</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873303</v>
+        <v>873407</v>
       </c>
       <c r="R7" t="n">
-        <v>7392314</v>
+        <v>7392275</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1277,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1303,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269182</v>
+        <v>123265715</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1331,19 +1337,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873578</v>
+        <v>873635</v>
       </c>
       <c r="R8" t="n">
-        <v>7392474</v>
+        <v>7392257</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1384,29 +1387,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269169</v>
+        <v>123269168</v>
       </c>
       <c r="B9" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873659</v>
+        <v>873634</v>
       </c>
       <c r="R9" t="n">
-        <v>7392406</v>
+        <v>7392446</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1509,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123265700</v>
+        <v>123269189</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,38 +1523,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873556</v>
+        <v>873683</v>
       </c>
       <c r="R10" t="n">
-        <v>7392510</v>
+        <v>7392341</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,25 +1598,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269186</v>
+        <v>123265708</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1645,19 +1651,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873664</v>
+        <v>873329</v>
       </c>
       <c r="R11" t="n">
-        <v>7392361</v>
+        <v>7392332</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1698,29 +1701,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269178</v>
+        <v>123265704</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,41 +1731,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873536</v>
+        <v>873421</v>
       </c>
       <c r="R12" t="n">
-        <v>7392501</v>
+        <v>7392291</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1804,26 +1803,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123265710</v>
+        <v>123269173</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1857,16 +1855,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873472</v>
+        <v>873348</v>
       </c>
       <c r="R13" t="n">
-        <v>7392425</v>
+        <v>7392214</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1907,28 +1908,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265701</v>
+        <v>123269186</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,34 +1943,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873422</v>
+        <v>873664</v>
       </c>
       <c r="R14" t="n">
-        <v>7392182</v>
+        <v>7392361</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2003,36 +2008,32 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269191</v>
+        <v>123269182</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2075,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873680</v>
+        <v>873578</v>
       </c>
       <c r="R15" t="n">
-        <v>7392337</v>
+        <v>7392474</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2138,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265703</v>
+        <v>123269174</v>
       </c>
       <c r="B16" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,38 +2151,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873327</v>
+        <v>873392</v>
       </c>
       <c r="R16" t="n">
-        <v>7392254</v>
+        <v>7392289</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2222,25 +2226,26 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269171</v>
+        <v>123269193</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873311</v>
+        <v>873639</v>
       </c>
       <c r="R17" t="n">
-        <v>7392309</v>
+        <v>7392268</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2319,11 +2324,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,7 +2351,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269173</v>
+        <v>123269172</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873348</v>
+        <v>873484</v>
       </c>
       <c r="R18" t="n">
-        <v>7392214</v>
+        <v>7392226</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269193</v>
+        <v>123265710</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2491,19 +2491,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873639</v>
+        <v>873472</v>
       </c>
       <c r="R19" t="n">
-        <v>7392268</v>
+        <v>7392425</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2544,29 +2541,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265714</v>
+        <v>123265698</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,25 +2571,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2603,10 +2599,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873664</v>
+        <v>873363</v>
       </c>
       <c r="R20" t="n">
-        <v>7392383</v>
+        <v>7392320</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2665,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123265706</v>
+        <v>123269169</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,38 +2673,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873363</v>
+        <v>873659</v>
       </c>
       <c r="R21" t="n">
-        <v>7392216</v>
+        <v>7392406</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2743,39 +2742,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269166</v>
+        <v>123265703</v>
       </c>
       <c r="B22" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,37 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873390</v>
+        <v>873327</v>
       </c>
       <c r="R22" t="n">
-        <v>7392303</v>
+        <v>7392254</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2859,29 +2851,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269167</v>
+        <v>123265692</v>
       </c>
       <c r="B23" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,41 +2881,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873630</v>
+        <v>873303</v>
       </c>
       <c r="R23" t="n">
-        <v>7392455</v>
+        <v>7392314</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2959,32 +2947,36 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269175</v>
+        <v>123269171</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3027,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873408</v>
+        <v>873311</v>
       </c>
       <c r="R24" t="n">
-        <v>7392282</v>
+        <v>7392309</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3063,6 +3055,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3090,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265699</v>
+        <v>123265694</v>
       </c>
       <c r="B25" t="n">
-        <v>90963</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,25 +3099,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3130,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873321</v>
+        <v>873473</v>
       </c>
       <c r="R25" t="n">
-        <v>7392268</v>
+        <v>7392448</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3166,6 +3163,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3192,7 +3194,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269180</v>
+        <v>123269191</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3235,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873544</v>
+        <v>873680</v>
       </c>
       <c r="R26" t="n">
-        <v>7392493</v>
+        <v>7392337</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3298,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123269189</v>
+        <v>123265714</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3332,19 +3334,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873683</v>
+        <v>873664</v>
       </c>
       <c r="R27" t="n">
-        <v>7392341</v>
+        <v>7392383</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,29 +3384,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269168</v>
+        <v>123265716</v>
       </c>
       <c r="B28" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3416,41 +3414,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873634</v>
+        <v>873655</v>
       </c>
       <c r="R28" t="n">
-        <v>7392446</v>
+        <v>7392246</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3491,29 +3486,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123269165</v>
+        <v>123265696</v>
       </c>
       <c r="B29" t="n">
-        <v>79876</v>
+        <v>90972</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,41 +3516,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873352</v>
+        <v>873644</v>
       </c>
       <c r="R29" t="n">
-        <v>7392213</v>
+        <v>7392267</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3597,29 +3588,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123265693</v>
+        <v>123265706</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,21 +3622,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3656,10 +3646,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873329</v>
+        <v>873363</v>
       </c>
       <c r="R30" t="n">
-        <v>7392331</v>
+        <v>7392216</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3696,7 +3686,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265709</v>
+        <v>123265705</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,21 +3729,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873407</v>
+        <v>873470</v>
       </c>
       <c r="R31" t="n">
-        <v>7392275</v>
+        <v>7392317</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3825,7 +3815,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265715</v>
+        <v>123265711</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3865,10 +3855,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873635</v>
+        <v>873476</v>
       </c>
       <c r="R32" t="n">
-        <v>7392257</v>
+        <v>7392450</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3927,7 +3917,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269172</v>
+        <v>123269188</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3970,10 +3960,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873484</v>
+        <v>873662</v>
       </c>
       <c r="R33" t="n">
-        <v>7392226</v>
+        <v>7392354</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4033,7 +4023,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123269176</v>
+        <v>123265707</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4067,19 +4057,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873462</v>
+        <v>873355</v>
       </c>
       <c r="R34" t="n">
-        <v>7392294</v>
+        <v>7392213</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4120,29 +4107,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265705</v>
+        <v>123269176</v>
       </c>
       <c r="B35" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,34 +4141,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873470</v>
+        <v>873462</v>
       </c>
       <c r="R35" t="n">
-        <v>7392317</v>
+        <v>7392294</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4223,28 +4212,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265708</v>
+        <v>123265700</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>90963</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4253,25 +4243,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4281,10 +4271,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873329</v>
+        <v>873556</v>
       </c>
       <c r="R36" t="n">
-        <v>7392332</v>
+        <v>7392510</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4343,10 +4333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265696</v>
+        <v>123265693</v>
       </c>
       <c r="B37" t="n">
-        <v>90972</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4359,21 +4349,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4373,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873644</v>
+        <v>873329</v>
       </c>
       <c r="R37" t="n">
-        <v>7392267</v>
+        <v>7392331</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4419,6 +4409,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4445,10 +4440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269174</v>
+        <v>123269167</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,25 +4452,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4488,10 +4483,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873392</v>
+        <v>873630</v>
       </c>
       <c r="R38" t="n">
-        <v>7392289</v>
+        <v>7392455</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4551,7 +4546,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265716</v>
+        <v>123269180</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4585,16 +4580,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873655</v>
+        <v>873544</v>
       </c>
       <c r="R39" t="n">
-        <v>7392246</v>
+        <v>7392493</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4635,25 +4633,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123265702</v>
+        <v>123265701</v>
       </c>
       <c r="B40" t="n">
         <v>57494</v>
@@ -4693,10 +4692,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873647</v>
+        <v>873422</v>
       </c>
       <c r="R40" t="n">
-        <v>7392305</v>
+        <v>7392182</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4733,7 +4732,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Avbarkad tall, färska spår</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4760,10 +4759,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123269188</v>
+        <v>123265702</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,37 +4775,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873662</v>
+        <v>873647</v>
       </c>
       <c r="R41" t="n">
-        <v>7392354</v>
+        <v>7392305</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4841,25 +4837,29 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265699</v>
+        <v>123265711</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873321</v>
+        <v>873476</v>
       </c>
       <c r="R2" t="n">
-        <v>7392268</v>
+        <v>7392450</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269165</v>
+        <v>123269188</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873352</v>
+        <v>873662</v>
       </c>
       <c r="R3" t="n">
-        <v>7392213</v>
+        <v>7392354</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123269178</v>
+        <v>123265703</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,41 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873536</v>
+        <v>873327</v>
       </c>
       <c r="R4" t="n">
-        <v>7392501</v>
+        <v>7392254</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -970,29 +967,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123269166</v>
+        <v>123265696</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,41 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873390</v>
+        <v>873644</v>
       </c>
       <c r="R5" t="n">
-        <v>7392303</v>
+        <v>7392267</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,26 +1069,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123269175</v>
+        <v>123265709</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1129,19 +1121,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873408</v>
+        <v>873407</v>
       </c>
       <c r="R6" t="n">
-        <v>7392282</v>
+        <v>7392275</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1182,26 +1171,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265709</v>
+        <v>123269176</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1235,16 +1223,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873407</v>
+        <v>873462</v>
       </c>
       <c r="R7" t="n">
-        <v>7392275</v>
+        <v>7392294</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1285,28 +1276,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265715</v>
+        <v>123269167</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,38 +1307,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873635</v>
+        <v>873630</v>
       </c>
       <c r="R8" t="n">
-        <v>7392257</v>
+        <v>7392455</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,28 +1382,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269168</v>
+        <v>123265692</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,41 +1413,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873634</v>
+        <v>873303</v>
       </c>
       <c r="R9" t="n">
-        <v>7392446</v>
+        <v>7392314</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1486,32 +1479,36 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269189</v>
+        <v>123269175</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1554,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873683</v>
+        <v>873408</v>
       </c>
       <c r="R10" t="n">
-        <v>7392341</v>
+        <v>7392282</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1617,7 +1614,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265708</v>
+        <v>123269182</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1651,16 +1648,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873329</v>
+        <v>873578</v>
       </c>
       <c r="R11" t="n">
-        <v>7392332</v>
+        <v>7392474</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1701,28 +1701,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265704</v>
+        <v>123269191</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,38 +1732,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873421</v>
+        <v>873680</v>
       </c>
       <c r="R12" t="n">
-        <v>7392291</v>
+        <v>7392337</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1803,28 +1807,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269173</v>
+        <v>123269165</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1864,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873348</v>
+        <v>873352</v>
       </c>
       <c r="R13" t="n">
-        <v>7392214</v>
+        <v>7392213</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1927,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269186</v>
+        <v>123269166</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1944,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873664</v>
+        <v>873390</v>
       </c>
       <c r="R14" t="n">
-        <v>7392361</v>
+        <v>7392303</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2033,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269182</v>
+        <v>123265699</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,41 +2050,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873578</v>
+        <v>873321</v>
       </c>
       <c r="R15" t="n">
-        <v>7392474</v>
+        <v>7392268</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2120,29 +2122,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269174</v>
+        <v>123265704</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,41 +2152,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873392</v>
+        <v>873421</v>
       </c>
       <c r="R16" t="n">
-        <v>7392289</v>
+        <v>7392291</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2226,19 +2224,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2351,7 +2348,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269172</v>
+        <v>123265707</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2385,19 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873484</v>
+        <v>873355</v>
       </c>
       <c r="R18" t="n">
-        <v>7392226</v>
+        <v>7392213</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2438,26 +2432,25 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123265710</v>
+        <v>123269180</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2491,16 +2484,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873472</v>
+        <v>873544</v>
       </c>
       <c r="R19" t="n">
-        <v>7392425</v>
+        <v>7392493</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2541,28 +2537,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265698</v>
+        <v>123269172</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,38 +2568,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873363</v>
+        <v>873484</v>
       </c>
       <c r="R20" t="n">
-        <v>7392320</v>
+        <v>7392226</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,28 +2643,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269169</v>
+        <v>123265705</v>
       </c>
       <c r="B21" t="n">
-        <v>79751</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,41 +2674,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873659</v>
+        <v>873470</v>
       </c>
       <c r="R21" t="n">
-        <v>7392406</v>
+        <v>7392317</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2748,29 +2746,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123265703</v>
+        <v>123269178</v>
       </c>
       <c r="B22" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,38 +2776,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873327</v>
+        <v>873536</v>
       </c>
       <c r="R22" t="n">
-        <v>7392254</v>
+        <v>7392501</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2851,28 +2851,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123265692</v>
+        <v>123265706</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,21 +2886,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2909,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873303</v>
+        <v>873363</v>
       </c>
       <c r="R23" t="n">
-        <v>7392314</v>
+        <v>7392216</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2949,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,7 +2977,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269171</v>
+        <v>123265710</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3010,19 +3011,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873311</v>
+        <v>873472</v>
       </c>
       <c r="R24" t="n">
-        <v>7392309</v>
+        <v>7392425</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3057,40 +3055,34 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265694</v>
+        <v>123269171</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,34 +3095,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873473</v>
+        <v>873311</v>
       </c>
       <c r="R25" t="n">
-        <v>7392448</v>
+        <v>7392309</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,7 +3162,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera bohål, några färska</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,28 +3171,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269191</v>
+        <v>123265700</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>90963</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,41 +3202,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873680</v>
+        <v>873556</v>
       </c>
       <c r="R26" t="n">
-        <v>7392337</v>
+        <v>7392510</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3281,26 +3274,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265714</v>
+        <v>123265715</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3340,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873664</v>
+        <v>873635</v>
       </c>
       <c r="R27" t="n">
-        <v>7392383</v>
+        <v>7392257</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3402,10 +3394,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265716</v>
+        <v>123265702</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,21 +3410,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3442,10 +3434,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873655</v>
+        <v>873647</v>
       </c>
       <c r="R28" t="n">
-        <v>7392246</v>
+        <v>7392305</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3478,6 +3470,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3504,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265696</v>
+        <v>123265708</v>
       </c>
       <c r="B29" t="n">
-        <v>90972</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3520,21 +3517,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873644</v>
+        <v>873329</v>
       </c>
       <c r="R29" t="n">
-        <v>7392267</v>
+        <v>7392332</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3606,7 +3603,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123265706</v>
+        <v>123269189</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3640,16 +3637,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873363</v>
+        <v>873683</v>
       </c>
       <c r="R30" t="n">
-        <v>7392216</v>
+        <v>7392341</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3684,39 +3684,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265705</v>
+        <v>123269174</v>
       </c>
       <c r="B31" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,34 +3725,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873470</v>
+        <v>873392</v>
       </c>
       <c r="R31" t="n">
-        <v>7392317</v>
+        <v>7392289</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3797,25 +3796,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265711</v>
+        <v>123265713</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873476</v>
+        <v>873664</v>
       </c>
       <c r="R32" t="n">
-        <v>7392450</v>
+        <v>7392383</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269188</v>
+        <v>123269168</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3929,25 +3929,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873662</v>
+        <v>873634</v>
       </c>
       <c r="R33" t="n">
-        <v>7392354</v>
+        <v>7392446</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265707</v>
+        <v>123265716</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873355</v>
+        <v>873655</v>
       </c>
       <c r="R34" t="n">
-        <v>7392213</v>
+        <v>7392246</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123269176</v>
+        <v>123265698</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4137,41 +4137,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873462</v>
+        <v>873363</v>
       </c>
       <c r="R35" t="n">
-        <v>7392294</v>
+        <v>7392320</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4212,29 +4209,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265700</v>
+        <v>123269173</v>
       </c>
       <c r="B36" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4243,38 +4239,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873556</v>
+        <v>873348</v>
       </c>
       <c r="R36" t="n">
-        <v>7392510</v>
+        <v>7392214</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4315,28 +4314,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265693</v>
+        <v>123269169</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4345,38 +4345,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873329</v>
+        <v>873659</v>
       </c>
       <c r="R37" t="n">
-        <v>7392331</v>
+        <v>7392406</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4411,39 +4414,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269167</v>
+        <v>123269186</v>
       </c>
       <c r="B38" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4452,25 +4451,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4483,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873630</v>
+        <v>873664</v>
       </c>
       <c r="R38" t="n">
-        <v>7392455</v>
+        <v>7392361</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4546,10 +4545,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269180</v>
+        <v>123265693</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4562,37 +4561,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873544</v>
+        <v>873329</v>
       </c>
       <c r="R39" t="n">
-        <v>7392493</v>
+        <v>7392331</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4627,35 +4623,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123265701</v>
+        <v>123265694</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,16 +4668,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873422</v>
+        <v>873473</v>
       </c>
       <c r="R40" t="n">
-        <v>7392182</v>
+        <v>7392448</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265702</v>
+        <v>123265701</v>
       </c>
       <c r="B41" t="n">
         <v>57494</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873647</v>
+        <v>873422</v>
       </c>
       <c r="R41" t="n">
-        <v>7392305</v>
+        <v>7392182</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Avbarkad tall, färska spår</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269188</v>
+        <v>123269167</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873662</v>
+        <v>873630</v>
       </c>
       <c r="R3" t="n">
-        <v>7392354</v>
+        <v>7392455</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265703</v>
+        <v>123269188</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873327</v>
+        <v>873662</v>
       </c>
       <c r="R4" t="n">
-        <v>7392254</v>
+        <v>7392354</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,28 +970,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265696</v>
+        <v>123265703</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873644</v>
+        <v>873327</v>
       </c>
       <c r="R5" t="n">
-        <v>7392267</v>
+        <v>7392254</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265709</v>
+        <v>123265696</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873407</v>
+        <v>873644</v>
       </c>
       <c r="R6" t="n">
-        <v>7392275</v>
+        <v>7392267</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1189,7 +1193,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269176</v>
+        <v>123265709</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1223,19 +1227,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873462</v>
+        <v>873407</v>
       </c>
       <c r="R7" t="n">
-        <v>7392294</v>
+        <v>7392275</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1276,29 +1277,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269167</v>
+        <v>123269176</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873630</v>
+        <v>873462</v>
       </c>
       <c r="R8" t="n">
-        <v>7392455</v>
+        <v>7392294</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269186</v>
+        <v>123265693</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4455,37 +4455,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873664</v>
+        <v>873329</v>
       </c>
       <c r="R38" t="n">
-        <v>7392361</v>
+        <v>7392331</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4520,32 +4517,36 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265693</v>
+        <v>123265694</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4585,10 +4586,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873329</v>
+        <v>873473</v>
       </c>
       <c r="R39" t="n">
-        <v>7392331</v>
+        <v>7392448</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4625,7 +4626,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,10 +4653,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123265694</v>
+        <v>123265701</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,16 +4669,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4692,10 +4693,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873473</v>
+        <v>873422</v>
       </c>
       <c r="R40" t="n">
-        <v>7392448</v>
+        <v>7392182</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4732,7 +4733,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera bohål, några färska</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4759,10 +4760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265701</v>
+        <v>123269186</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,34 +4776,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873422</v>
+        <v>873664</v>
       </c>
       <c r="R41" t="n">
-        <v>7392182</v>
+        <v>7392361</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4837,29 +4841,25 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265711</v>
+        <v>123269171</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873476</v>
+        <v>873311</v>
       </c>
       <c r="R2" t="n">
-        <v>7392450</v>
+        <v>7392309</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,34 +756,40 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269167</v>
+        <v>123269169</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873630</v>
+        <v>873659</v>
       </c>
       <c r="R3" t="n">
-        <v>7392455</v>
+        <v>7392406</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123269188</v>
+        <v>123265698</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,41 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873662</v>
+        <v>873363</v>
       </c>
       <c r="R4" t="n">
-        <v>7392354</v>
+        <v>7392320</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -970,29 +976,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265703</v>
+        <v>123265692</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873327</v>
+        <v>873303</v>
       </c>
       <c r="R5" t="n">
-        <v>7392254</v>
+        <v>7392314</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1065,6 +1070,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265696</v>
+        <v>123265694</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873644</v>
+        <v>873473</v>
       </c>
       <c r="R6" t="n">
-        <v>7392267</v>
+        <v>7392448</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1167,6 +1177,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265709</v>
+        <v>123269167</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,38 +1220,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873407</v>
+        <v>873630</v>
       </c>
       <c r="R7" t="n">
-        <v>7392275</v>
+        <v>7392455</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1277,28 +1295,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269176</v>
+        <v>123269191</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873462</v>
+        <v>873680</v>
       </c>
       <c r="R8" t="n">
-        <v>7392294</v>
+        <v>7392337</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1401,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265692</v>
+        <v>123269188</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,34 +1436,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873303</v>
+        <v>873662</v>
       </c>
       <c r="R9" t="n">
-        <v>7392314</v>
+        <v>7392354</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1479,39 +1501,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269175</v>
+        <v>123269193</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873408</v>
+        <v>873639</v>
       </c>
       <c r="R10" t="n">
-        <v>7392282</v>
+        <v>7392268</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1614,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269182</v>
+        <v>123269176</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873578</v>
+        <v>873462</v>
       </c>
       <c r="R11" t="n">
-        <v>7392474</v>
+        <v>7392294</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1720,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269191</v>
+        <v>123269172</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873680</v>
+        <v>873484</v>
       </c>
       <c r="R12" t="n">
-        <v>7392337</v>
+        <v>7392226</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1826,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269165</v>
+        <v>123269175</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873352</v>
+        <v>873408</v>
       </c>
       <c r="R13" t="n">
-        <v>7392213</v>
+        <v>7392282</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1932,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269166</v>
+        <v>123265703</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>79754</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,37 +1966,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873390</v>
+        <v>873327</v>
       </c>
       <c r="R14" t="n">
-        <v>7392303</v>
+        <v>7392254</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2019,29 +2034,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123265699</v>
+        <v>123265693</v>
       </c>
       <c r="B15" t="n">
-        <v>90963</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,25 +2064,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2078,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873321</v>
+        <v>873329</v>
       </c>
       <c r="R15" t="n">
-        <v>7392268</v>
+        <v>7392331</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2114,6 +2128,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265704</v>
+        <v>123265710</v>
       </c>
       <c r="B16" t="n">
-        <v>79751</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2180,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873421</v>
+        <v>873472</v>
       </c>
       <c r="R16" t="n">
-        <v>7392291</v>
+        <v>7392425</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2242,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269193</v>
+        <v>123269182</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873639</v>
+        <v>873578</v>
       </c>
       <c r="R17" t="n">
-        <v>7392268</v>
+        <v>7392474</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2348,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265707</v>
+        <v>123265708</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873355</v>
+        <v>873329</v>
       </c>
       <c r="R18" t="n">
-        <v>7392213</v>
+        <v>7392332</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2450,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269180</v>
+        <v>123269165</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2462,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2493,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873544</v>
+        <v>873352</v>
       </c>
       <c r="R19" t="n">
-        <v>7392493</v>
+        <v>7392213</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2556,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269172</v>
+        <v>123269173</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873484</v>
+        <v>873348</v>
       </c>
       <c r="R20" t="n">
-        <v>7392226</v>
+        <v>7392214</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2662,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123265705</v>
+        <v>123269178</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2678,34 +2697,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873470</v>
+        <v>873536</v>
       </c>
       <c r="R21" t="n">
-        <v>7392317</v>
+        <v>7392501</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2746,28 +2768,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269178</v>
+        <v>123269174</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873536</v>
+        <v>873392</v>
       </c>
       <c r="R22" t="n">
-        <v>7392501</v>
+        <v>7392289</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2870,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123265706</v>
+        <v>123265711</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873363</v>
+        <v>873476</v>
       </c>
       <c r="R23" t="n">
-        <v>7392216</v>
+        <v>7392450</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2946,11 +2969,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,10 +2995,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265710</v>
+        <v>123265716</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873472</v>
+        <v>873655</v>
       </c>
       <c r="R24" t="n">
-        <v>7392425</v>
+        <v>7392246</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3079,10 +3097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123269171</v>
+        <v>123265704</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79754</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,41 +3109,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873311</v>
+        <v>873421</v>
       </c>
       <c r="R25" t="n">
-        <v>7392309</v>
+        <v>7392291</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3160,40 +3175,34 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265700</v>
+        <v>123265705</v>
       </c>
       <c r="B26" t="n">
-        <v>90963</v>
+        <v>78505</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3202,25 +3211,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3230,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873556</v>
+        <v>873470</v>
       </c>
       <c r="R26" t="n">
-        <v>7392510</v>
+        <v>7392317</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3292,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265715</v>
+        <v>123265714</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873635</v>
+        <v>873664</v>
       </c>
       <c r="R27" t="n">
-        <v>7392257</v>
+        <v>7392383</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3394,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265702</v>
+        <v>123265706</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3410,21 +3419,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3434,10 +3443,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873647</v>
+        <v>873363</v>
       </c>
       <c r="R28" t="n">
-        <v>7392305</v>
+        <v>7392216</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3474,7 +3483,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Avbarkad tall, färska spår</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265708</v>
+        <v>123265707</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3541,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873329</v>
+        <v>873355</v>
       </c>
       <c r="R29" t="n">
-        <v>7392332</v>
+        <v>7392213</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3603,10 +3612,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269189</v>
+        <v>123265696</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>90975</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3619,37 +3628,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873683</v>
+        <v>873644</v>
       </c>
       <c r="R30" t="n">
-        <v>7392341</v>
+        <v>7392267</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3690,29 +3696,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123269174</v>
+        <v>123269168</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,25 +3726,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873392</v>
+        <v>873634</v>
       </c>
       <c r="R31" t="n">
-        <v>7392289</v>
+        <v>7392446</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3815,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265713</v>
+        <v>123265702</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,21 +3836,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873664</v>
+        <v>873647</v>
       </c>
       <c r="R32" t="n">
-        <v>7392383</v>
+        <v>7392305</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3891,6 +3896,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269168</v>
+        <v>123265699</v>
       </c>
       <c r="B33" t="n">
-        <v>79876</v>
+        <v>90966</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3933,37 +3943,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873634</v>
+        <v>873321</v>
       </c>
       <c r="R33" t="n">
-        <v>7392446</v>
+        <v>7392268</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4004,29 +4011,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265716</v>
+        <v>123265701</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4039,21 +4045,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4063,10 +4069,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873655</v>
+        <v>873422</v>
       </c>
       <c r="R34" t="n">
-        <v>7392246</v>
+        <v>7392182</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4099,6 +4105,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4125,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265698</v>
+        <v>123269189</v>
       </c>
       <c r="B35" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4137,38 +4148,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873363</v>
+        <v>873683</v>
       </c>
       <c r="R35" t="n">
-        <v>7392320</v>
+        <v>7392341</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4209,28 +4223,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269173</v>
+        <v>123265709</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4261,19 +4276,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873348</v>
+        <v>873407</v>
       </c>
       <c r="R36" t="n">
-        <v>7392214</v>
+        <v>7392275</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4314,29 +4326,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123269169</v>
+        <v>123269186</v>
       </c>
       <c r="B37" t="n">
-        <v>79751</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4345,25 +4356,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4376,10 +4387,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873659</v>
+        <v>873664</v>
       </c>
       <c r="R37" t="n">
-        <v>7392406</v>
+        <v>7392361</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4439,10 +4450,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265693</v>
+        <v>123265715</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4455,21 +4466,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4479,10 +4490,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873329</v>
+        <v>873635</v>
       </c>
       <c r="R38" t="n">
-        <v>7392331</v>
+        <v>7392257</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4515,11 +4526,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4546,10 +4552,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265694</v>
+        <v>123265700</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>90966</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4558,25 +4564,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4586,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873473</v>
+        <v>873556</v>
       </c>
       <c r="R39" t="n">
-        <v>7392448</v>
+        <v>7392510</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4622,11 +4628,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4653,10 +4654,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123265701</v>
+        <v>123269166</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>79879</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4665,38 +4666,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873422</v>
+        <v>873390</v>
       </c>
       <c r="R40" t="n">
-        <v>7392182</v>
+        <v>7392303</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4731,39 +4735,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123269186</v>
+        <v>123269180</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873664</v>
+        <v>873544</v>
       </c>
       <c r="R41" t="n">
-        <v>7392361</v>
+        <v>7392493</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269171</v>
+        <v>123269176</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873311</v>
+        <v>873462</v>
       </c>
       <c r="R2" t="n">
-        <v>7392309</v>
+        <v>7392294</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269169</v>
+        <v>123265714</v>
       </c>
       <c r="B3" t="n">
-        <v>79754</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873659</v>
+        <v>873664</v>
       </c>
       <c r="R3" t="n">
-        <v>7392406</v>
+        <v>7392383</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -873,29 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265698</v>
+        <v>123265704</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>79756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873363</v>
+        <v>873421</v>
       </c>
       <c r="R4" t="n">
-        <v>7392320</v>
+        <v>7392291</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265694</v>
+        <v>123265701</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,16 +1108,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1141,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873473</v>
+        <v>873422</v>
       </c>
       <c r="R6" t="n">
-        <v>7392448</v>
+        <v>7392182</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1181,7 +1172,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera bohål, några färska</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269167</v>
+        <v>123269188</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873630</v>
+        <v>873662</v>
       </c>
       <c r="R7" t="n">
-        <v>7392455</v>
+        <v>7392354</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269191</v>
+        <v>123265703</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>79756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,41 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873680</v>
+        <v>873327</v>
       </c>
       <c r="R8" t="n">
-        <v>7392337</v>
+        <v>7392254</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1401,29 +1389,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269188</v>
+        <v>123265696</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,37 +1423,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873662</v>
+        <v>873644</v>
       </c>
       <c r="R9" t="n">
-        <v>7392354</v>
+        <v>7392267</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1507,29 +1491,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269193</v>
+        <v>123269186</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873639</v>
+        <v>873664</v>
       </c>
       <c r="R10" t="n">
-        <v>7392268</v>
+        <v>7392361</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1632,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269176</v>
+        <v>123265700</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>90968</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,41 +1627,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873462</v>
+        <v>873556</v>
       </c>
       <c r="R11" t="n">
-        <v>7392294</v>
+        <v>7392510</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1719,29 +1699,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269172</v>
+        <v>123269178</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873484</v>
+        <v>873536</v>
       </c>
       <c r="R12" t="n">
-        <v>7392226</v>
+        <v>7392501</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1844,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269175</v>
+        <v>123269182</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873408</v>
+        <v>873578</v>
       </c>
       <c r="R13" t="n">
-        <v>7392282</v>
+        <v>7392474</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1950,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265703</v>
+        <v>123265698</v>
       </c>
       <c r="B14" t="n">
-        <v>79754</v>
+        <v>79881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R14" t="n">
-        <v>7392254</v>
+        <v>7392320</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2052,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123265693</v>
+        <v>123269168</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>79881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,38 +2043,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873329</v>
+        <v>873634</v>
       </c>
       <c r="R15" t="n">
-        <v>7392331</v>
+        <v>7392446</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2130,39 +2112,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265710</v>
+        <v>123265708</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873472</v>
+        <v>873329</v>
       </c>
       <c r="R16" t="n">
-        <v>7392425</v>
+        <v>7392332</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2261,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269182</v>
+        <v>123269174</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873578</v>
+        <v>873392</v>
       </c>
       <c r="R17" t="n">
-        <v>7392474</v>
+        <v>7392289</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2367,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265708</v>
+        <v>123265716</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873329</v>
+        <v>873655</v>
       </c>
       <c r="R18" t="n">
-        <v>7392332</v>
+        <v>7392246</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2472,7 +2450,7 @@
         <v>123269165</v>
       </c>
       <c r="B19" t="n">
-        <v>79879</v>
+        <v>79881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269173</v>
+        <v>123265693</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,37 +2569,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873348</v>
+        <v>873329</v>
       </c>
       <c r="R20" t="n">
-        <v>7392214</v>
+        <v>7392331</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,35 +2631,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269178</v>
+        <v>123265707</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,19 +2694,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873536</v>
+        <v>873355</v>
       </c>
       <c r="R21" t="n">
-        <v>7392501</v>
+        <v>7392213</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2768,29 +2744,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269174</v>
+        <v>123269166</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2774,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873392</v>
+        <v>873390</v>
       </c>
       <c r="R22" t="n">
-        <v>7392289</v>
+        <v>7392303</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2893,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123265711</v>
+        <v>123269173</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,16 +2902,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873476</v>
+        <v>873348</v>
       </c>
       <c r="R23" t="n">
-        <v>7392450</v>
+        <v>7392214</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2977,28 +2955,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265716</v>
+        <v>123265709</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873655</v>
+        <v>873407</v>
       </c>
       <c r="R24" t="n">
-        <v>7392246</v>
+        <v>7392275</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3097,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265704</v>
+        <v>123265699</v>
       </c>
       <c r="B25" t="n">
-        <v>79754</v>
+        <v>90968</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873421</v>
+        <v>873321</v>
       </c>
       <c r="R25" t="n">
-        <v>7392291</v>
+        <v>7392268</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3199,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265705</v>
+        <v>123269171</v>
       </c>
       <c r="B26" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,34 +3194,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873470</v>
+        <v>873311</v>
       </c>
       <c r="R26" t="n">
-        <v>7392317</v>
+        <v>7392309</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3277,34 +3259,40 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265714</v>
+        <v>123269169</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>79756</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,38 +3301,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R27" t="n">
-        <v>7392383</v>
+        <v>7392406</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3385,28 +3376,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265706</v>
+        <v>123269189</v>
       </c>
       <c r="B28" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3437,16 +3429,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873363</v>
+        <v>873683</v>
       </c>
       <c r="R28" t="n">
-        <v>7392216</v>
+        <v>7392341</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3481,39 +3476,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265707</v>
+        <v>123265706</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873355</v>
+        <v>873363</v>
       </c>
       <c r="R29" t="n">
-        <v>7392213</v>
+        <v>7392216</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3586,6 +3577,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3612,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123265696</v>
+        <v>123269180</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3628,34 +3624,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873644</v>
+        <v>873544</v>
       </c>
       <c r="R30" t="n">
-        <v>7392267</v>
+        <v>7392493</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3696,28 +3695,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123269168</v>
+        <v>123269167</v>
       </c>
       <c r="B31" t="n">
-        <v>79879</v>
+        <v>79881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873634</v>
+        <v>873630</v>
       </c>
       <c r="R31" t="n">
-        <v>7392446</v>
+        <v>7392455</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265702</v>
+        <v>123269175</v>
       </c>
       <c r="B32" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3836,34 +3836,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873647</v>
+        <v>873408</v>
       </c>
       <c r="R32" t="n">
-        <v>7392305</v>
+        <v>7392282</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3898,39 +3901,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265699</v>
+        <v>123265694</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,25 +3938,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873321</v>
+        <v>873473</v>
       </c>
       <c r="R33" t="n">
-        <v>7392268</v>
+        <v>7392448</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4003,6 +4002,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4029,10 +4033,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265701</v>
+        <v>123265715</v>
       </c>
       <c r="B34" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,21 +4049,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4069,10 +4073,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873422</v>
+        <v>873635</v>
       </c>
       <c r="R34" t="n">
-        <v>7392182</v>
+        <v>7392257</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4105,11 +4109,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4136,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123269189</v>
+        <v>123265711</v>
       </c>
       <c r="B35" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,19 +4169,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873683</v>
+        <v>873476</v>
       </c>
       <c r="R35" t="n">
-        <v>7392341</v>
+        <v>7392450</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4223,29 +4219,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265709</v>
+        <v>123265710</v>
       </c>
       <c r="B36" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4282,10 +4277,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873407</v>
+        <v>873472</v>
       </c>
       <c r="R36" t="n">
-        <v>7392275</v>
+        <v>7392425</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4344,10 +4339,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123269186</v>
+        <v>123265705</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>78507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4360,37 +4355,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873664</v>
+        <v>873470</v>
       </c>
       <c r="R37" t="n">
-        <v>7392361</v>
+        <v>7392317</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4431,29 +4423,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265715</v>
+        <v>123265702</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4490,10 +4481,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873635</v>
+        <v>873647</v>
       </c>
       <c r="R38" t="n">
-        <v>7392257</v>
+        <v>7392305</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4526,6 +4517,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4552,10 +4548,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265700</v>
+        <v>123269191</v>
       </c>
       <c r="B39" t="n">
-        <v>90966</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4564,38 +4560,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873556</v>
+        <v>873680</v>
       </c>
       <c r="R39" t="n">
-        <v>7392510</v>
+        <v>7392337</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4636,28 +4635,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269166</v>
+        <v>123269193</v>
       </c>
       <c r="B40" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4666,25 +4666,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873390</v>
+        <v>873639</v>
       </c>
       <c r="R40" t="n">
-        <v>7392303</v>
+        <v>7392268</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123269180</v>
+        <v>123269172</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873544</v>
+        <v>873484</v>
       </c>
       <c r="R41" t="n">
-        <v>7392493</v>
+        <v>7392226</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265696</v>
+        <v>123269186</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,34 +1423,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873644</v>
+        <v>873664</v>
       </c>
       <c r="R9" t="n">
-        <v>7392267</v>
+        <v>7392361</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,28 +1494,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269186</v>
+        <v>123265696</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,37 +1529,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873664</v>
+        <v>873644</v>
       </c>
       <c r="R10" t="n">
-        <v>7392361</v>
+        <v>7392267</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1596,19 +1597,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269176</v>
+        <v>123269175</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873462</v>
+        <v>873408</v>
       </c>
       <c r="R2" t="n">
-        <v>7392294</v>
+        <v>7392282</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123265714</v>
+        <v>123269169</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>79757</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R3" t="n">
-        <v>7392383</v>
+        <v>7392406</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,28 +868,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265704</v>
+        <v>123265708</v>
       </c>
       <c r="B4" t="n">
-        <v>79756</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873421</v>
+        <v>873329</v>
       </c>
       <c r="R4" t="n">
-        <v>7392291</v>
+        <v>7392332</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265692</v>
+        <v>123269193</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,34 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873303</v>
+        <v>873639</v>
       </c>
       <c r="R5" t="n">
-        <v>7392314</v>
+        <v>7392268</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1063,39 +1070,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265701</v>
+        <v>123265693</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,16 +1111,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1132,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873422</v>
+        <v>873329</v>
       </c>
       <c r="R6" t="n">
-        <v>7392182</v>
+        <v>7392331</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1172,7 +1175,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269188</v>
+        <v>123265694</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,37 +1218,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873662</v>
+        <v>873473</v>
       </c>
       <c r="R7" t="n">
-        <v>7392354</v>
+        <v>7392448</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,35 +1280,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265703</v>
+        <v>123265706</v>
       </c>
       <c r="B8" t="n">
-        <v>79756</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1321,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R8" t="n">
-        <v>7392254</v>
+        <v>7392216</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1381,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269186</v>
+        <v>123265699</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>90974</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,41 +1428,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873664</v>
+        <v>873321</v>
       </c>
       <c r="R9" t="n">
-        <v>7392361</v>
+        <v>7392268</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1494,29 +1500,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123265696</v>
+        <v>123265698</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>79882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1530,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873644</v>
+        <v>873363</v>
       </c>
       <c r="R10" t="n">
-        <v>7392267</v>
+        <v>7392320</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1615,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265700</v>
+        <v>123265709</v>
       </c>
       <c r="B11" t="n">
-        <v>90968</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,25 +1632,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873556</v>
+        <v>873407</v>
       </c>
       <c r="R11" t="n">
-        <v>7392510</v>
+        <v>7392275</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1717,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269178</v>
+        <v>123269182</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873536</v>
+        <v>873578</v>
       </c>
       <c r="R12" t="n">
-        <v>7392501</v>
+        <v>7392474</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1816,17 +1821,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269182</v>
+        <v>123269173</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873578</v>
+        <v>873348</v>
       </c>
       <c r="R13" t="n">
-        <v>7392474</v>
+        <v>7392214</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265698</v>
+        <v>123269189</v>
       </c>
       <c r="B14" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,38 +1946,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873363</v>
+        <v>873683</v>
       </c>
       <c r="R14" t="n">
-        <v>7392320</v>
+        <v>7392341</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2013,28 +2021,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269168</v>
+        <v>123269166</v>
       </c>
       <c r="B15" t="n">
-        <v>79881</v>
+        <v>79882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873634</v>
+        <v>873390</v>
       </c>
       <c r="R15" t="n">
-        <v>7392446</v>
+        <v>7392303</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2137,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265708</v>
+        <v>123265701</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,21 +2162,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873329</v>
+        <v>873422</v>
       </c>
       <c r="R16" t="n">
-        <v>7392332</v>
+        <v>7392182</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,6 +2222,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269174</v>
+        <v>123265710</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,19 +2287,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873392</v>
+        <v>873472</v>
       </c>
       <c r="R17" t="n">
-        <v>7392289</v>
+        <v>7392425</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2326,29 +2337,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265716</v>
+        <v>123269168</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,38 +2367,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873655</v>
+        <v>873634</v>
       </c>
       <c r="R18" t="n">
-        <v>7392246</v>
+        <v>7392446</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2429,28 +2442,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269165</v>
+        <v>123269174</v>
       </c>
       <c r="B19" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2459,25 +2473,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873352</v>
+        <v>873392</v>
       </c>
       <c r="R19" t="n">
-        <v>7392213</v>
+        <v>7392289</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2553,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265693</v>
+        <v>123269188</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,34 +2583,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873329</v>
+        <v>873662</v>
       </c>
       <c r="R20" t="n">
-        <v>7392331</v>
+        <v>7392354</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2631,39 +2648,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123265707</v>
+        <v>123265711</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873355</v>
+        <v>873476</v>
       </c>
       <c r="R21" t="n">
-        <v>7392213</v>
+        <v>7392450</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2762,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269166</v>
+        <v>123265714</v>
       </c>
       <c r="B22" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,41 +2787,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873390</v>
+        <v>873664</v>
       </c>
       <c r="R22" t="n">
-        <v>7392303</v>
+        <v>7392383</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2849,29 +2859,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269173</v>
+        <v>123269165</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,25 +2889,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,10 +2920,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873348</v>
+        <v>873352</v>
       </c>
       <c r="R23" t="n">
-        <v>7392214</v>
+        <v>7392213</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2974,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265709</v>
+        <v>123265716</v>
       </c>
       <c r="B24" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3014,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873407</v>
+        <v>873655</v>
       </c>
       <c r="R24" t="n">
-        <v>7392275</v>
+        <v>7392246</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3076,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265699</v>
+        <v>123265707</v>
       </c>
       <c r="B25" t="n">
-        <v>90968</v>
+        <v>78772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,25 +3097,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873321</v>
+        <v>873355</v>
       </c>
       <c r="R25" t="n">
-        <v>7392268</v>
+        <v>7392213</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3178,10 +3187,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269171</v>
+        <v>123269172</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3221,10 +3230,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873311</v>
+        <v>873484</v>
       </c>
       <c r="R26" t="n">
-        <v>7392309</v>
+        <v>7392226</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3257,11 +3266,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,10 +3293,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123269169</v>
+        <v>123265703</v>
       </c>
       <c r="B27" t="n">
-        <v>79756</v>
+        <v>79757</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,19 +3327,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873659</v>
+        <v>873327</v>
       </c>
       <c r="R27" t="n">
-        <v>7392406</v>
+        <v>7392254</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3376,29 +3377,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269189</v>
+        <v>123265705</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,37 +3411,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873683</v>
+        <v>873470</v>
       </c>
       <c r="R28" t="n">
-        <v>7392341</v>
+        <v>7392317</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3482,29 +3479,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265706</v>
+        <v>123265715</v>
       </c>
       <c r="B29" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3541,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873363</v>
+        <v>873635</v>
       </c>
       <c r="R29" t="n">
-        <v>7392216</v>
+        <v>7392257</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3577,11 +3573,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3599,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269180</v>
+        <v>123265700</v>
       </c>
       <c r="B30" t="n">
-        <v>78771</v>
+        <v>90974</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,41 +3611,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873544</v>
+        <v>873556</v>
       </c>
       <c r="R30" t="n">
-        <v>7392493</v>
+        <v>7392510</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3695,29 +3683,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123269167</v>
+        <v>123265696</v>
       </c>
       <c r="B31" t="n">
-        <v>79881</v>
+        <v>90983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,41 +3713,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873630</v>
+        <v>873644</v>
       </c>
       <c r="R31" t="n">
-        <v>7392455</v>
+        <v>7392267</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3801,29 +3785,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123269175</v>
+        <v>123269191</v>
       </c>
       <c r="B32" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3863,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873408</v>
+        <v>873680</v>
       </c>
       <c r="R32" t="n">
-        <v>7392282</v>
+        <v>7392337</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3919,17 +3902,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265694</v>
+        <v>123269176</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,34 +3925,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873473</v>
+        <v>873462</v>
       </c>
       <c r="R33" t="n">
-        <v>7392448</v>
+        <v>7392294</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4004,39 +3990,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265715</v>
+        <v>123265704</v>
       </c>
       <c r="B34" t="n">
-        <v>78771</v>
+        <v>79757</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,25 +4027,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4073,10 +4055,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873635</v>
+        <v>873421</v>
       </c>
       <c r="R34" t="n">
-        <v>7392257</v>
+        <v>7392291</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4135,10 +4117,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265711</v>
+        <v>123265692</v>
       </c>
       <c r="B35" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4151,21 +4133,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4175,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873476</v>
+        <v>873303</v>
       </c>
       <c r="R35" t="n">
-        <v>7392450</v>
+        <v>7392314</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4211,6 +4193,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4237,10 +4224,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265710</v>
+        <v>123269171</v>
       </c>
       <c r="B36" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4271,16 +4258,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873472</v>
+        <v>873311</v>
       </c>
       <c r="R36" t="n">
-        <v>7392425</v>
+        <v>7392309</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4315,34 +4305,40 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265705</v>
+        <v>123269180</v>
       </c>
       <c r="B37" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873470</v>
+        <v>873544</v>
       </c>
       <c r="R37" t="n">
-        <v>7392317</v>
+        <v>7392493</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4423,28 +4422,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265702</v>
+        <v>123269167</v>
       </c>
       <c r="B38" t="n">
-        <v>57497</v>
+        <v>79882</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,38 +4453,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873647</v>
+        <v>873630</v>
       </c>
       <c r="R38" t="n">
-        <v>7392305</v>
+        <v>7392455</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4519,39 +4522,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269191</v>
+        <v>123269178</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4591,10 +4590,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873680</v>
+        <v>873536</v>
       </c>
       <c r="R39" t="n">
-        <v>7392337</v>
+        <v>7392501</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4647,17 +4646,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269193</v>
+        <v>123269186</v>
       </c>
       <c r="B40" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4697,10 +4696,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873639</v>
+        <v>873664</v>
       </c>
       <c r="R40" t="n">
-        <v>7392268</v>
+        <v>7392361</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4753,17 +4752,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123269172</v>
+        <v>123265702</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,37 +4775,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873484</v>
+        <v>873647</v>
       </c>
       <c r="R41" t="n">
-        <v>7392226</v>
+        <v>7392305</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4841,25 +4837,29 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269175</v>
+        <v>123265711</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,19 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873408</v>
+        <v>873476</v>
       </c>
       <c r="R2" t="n">
-        <v>7392282</v>
+        <v>7392450</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,19 +759,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +780,7 @@
         <v>123269169</v>
       </c>
       <c r="B3" t="n">
-        <v>79757</v>
+        <v>79760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265708</v>
+        <v>123269165</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +895,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873329</v>
+        <v>873352</v>
       </c>
       <c r="R4" t="n">
-        <v>7392332</v>
+        <v>7392213</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -971,28 +970,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123269193</v>
+        <v>123269173</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873639</v>
+        <v>873348</v>
       </c>
       <c r="R5" t="n">
-        <v>7392268</v>
+        <v>7392214</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265693</v>
+        <v>123265716</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873329</v>
+        <v>873655</v>
       </c>
       <c r="R6" t="n">
-        <v>7392331</v>
+        <v>7392246</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1171,11 +1171,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265694</v>
+        <v>123265707</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,21 +1213,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873473</v>
+        <v>873355</v>
       </c>
       <c r="R7" t="n">
-        <v>7392448</v>
+        <v>7392213</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1278,11 +1273,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265706</v>
+        <v>123265698</v>
       </c>
       <c r="B8" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,25 +1311,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,7 +1342,7 @@
         <v>873363</v>
       </c>
       <c r="R8" t="n">
-        <v>7392216</v>
+        <v>7392320</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1385,11 +1375,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265699</v>
+        <v>123265705</v>
       </c>
       <c r="B9" t="n">
-        <v>90974</v>
+        <v>78511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1413,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873321</v>
+        <v>873470</v>
       </c>
       <c r="R9" t="n">
-        <v>7392268</v>
+        <v>7392317</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1518,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123265698</v>
+        <v>123269175</v>
       </c>
       <c r="B10" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,38 +1515,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873363</v>
+        <v>873408</v>
       </c>
       <c r="R10" t="n">
-        <v>7392320</v>
+        <v>7392282</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1602,28 +1590,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265709</v>
+        <v>123265692</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873407</v>
+        <v>873303</v>
       </c>
       <c r="R11" t="n">
-        <v>7392275</v>
+        <v>7392314</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1696,6 +1685,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269182</v>
+        <v>123269172</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873578</v>
+        <v>873484</v>
       </c>
       <c r="R12" t="n">
-        <v>7392474</v>
+        <v>7392226</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1821,17 +1815,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269173</v>
+        <v>123265714</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,19 +1856,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873348</v>
+        <v>873664</v>
       </c>
       <c r="R13" t="n">
-        <v>7392214</v>
+        <v>7392383</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1915,29 +1906,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269189</v>
+        <v>123269166</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873683</v>
+        <v>873390</v>
       </c>
       <c r="R14" t="n">
-        <v>7392341</v>
+        <v>7392303</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2033,17 +2023,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269166</v>
+        <v>123269182</v>
       </c>
       <c r="B15" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,25 +2042,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873390</v>
+        <v>873578</v>
       </c>
       <c r="R15" t="n">
-        <v>7392303</v>
+        <v>7392474</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2146,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265701</v>
+        <v>123265706</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>78775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,21 +2152,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2176,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873422</v>
+        <v>873363</v>
       </c>
       <c r="R16" t="n">
-        <v>7392182</v>
+        <v>7392216</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2226,7 +2216,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,10 +2243,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265710</v>
+        <v>123269188</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,16 +2277,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873472</v>
+        <v>873662</v>
       </c>
       <c r="R17" t="n">
-        <v>7392425</v>
+        <v>7392354</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2337,28 +2330,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269168</v>
+        <v>123269191</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,25 +2361,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873634</v>
+        <v>873680</v>
       </c>
       <c r="R18" t="n">
-        <v>7392446</v>
+        <v>7392337</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2461,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269174</v>
+        <v>123265708</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,19 +2489,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873392</v>
+        <v>873329</v>
       </c>
       <c r="R19" t="n">
-        <v>7392289</v>
+        <v>7392332</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2548,29 +2539,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269188</v>
+        <v>123269167</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2569,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2610,10 +2600,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873662</v>
+        <v>873630</v>
       </c>
       <c r="R20" t="n">
-        <v>7392354</v>
+        <v>7392455</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,17 +2656,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123265711</v>
+        <v>123265700</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2675,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873476</v>
+        <v>873556</v>
       </c>
       <c r="R21" t="n">
-        <v>7392450</v>
+        <v>7392510</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2775,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123265714</v>
+        <v>123269178</v>
       </c>
       <c r="B22" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,16 +2799,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873664</v>
+        <v>873536</v>
       </c>
       <c r="R22" t="n">
-        <v>7392383</v>
+        <v>7392501</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2859,28 +2852,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269165</v>
+        <v>123269171</v>
       </c>
       <c r="B23" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,25 +2883,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2920,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873352</v>
+        <v>873311</v>
       </c>
       <c r="R23" t="n">
-        <v>7392213</v>
+        <v>7392309</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2956,6 +2950,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2983,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265716</v>
+        <v>123269193</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,16 +3016,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873655</v>
+        <v>873639</v>
       </c>
       <c r="R24" t="n">
-        <v>7392246</v>
+        <v>7392268</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,28 +3069,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265707</v>
+        <v>123269186</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,16 +3122,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873355</v>
+        <v>873664</v>
       </c>
       <c r="R25" t="n">
-        <v>7392213</v>
+        <v>7392361</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3169,28 +3175,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269172</v>
+        <v>123265715</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3221,19 +3228,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873484</v>
+        <v>873635</v>
       </c>
       <c r="R26" t="n">
-        <v>7392226</v>
+        <v>7392257</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3274,29 +3278,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265703</v>
+        <v>123265704</v>
       </c>
       <c r="B27" t="n">
-        <v>79757</v>
+        <v>79760</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873327</v>
+        <v>873421</v>
       </c>
       <c r="R27" t="n">
-        <v>7392254</v>
+        <v>7392291</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3395,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265705</v>
+        <v>123265696</v>
       </c>
       <c r="B28" t="n">
-        <v>78508</v>
+        <v>90986</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,21 +3414,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3435,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873470</v>
+        <v>873644</v>
       </c>
       <c r="R28" t="n">
-        <v>7392317</v>
+        <v>7392267</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265715</v>
+        <v>123265703</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>79760</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3509,25 +3512,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3537,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873635</v>
+        <v>873327</v>
       </c>
       <c r="R29" t="n">
-        <v>7392257</v>
+        <v>7392254</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3599,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123265700</v>
+        <v>123269180</v>
       </c>
       <c r="B30" t="n">
-        <v>90974</v>
+        <v>78775</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3611,38 +3614,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873556</v>
+        <v>873544</v>
       </c>
       <c r="R30" t="n">
-        <v>7392510</v>
+        <v>7392493</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3683,28 +3689,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265696</v>
+        <v>123265694</v>
       </c>
       <c r="B31" t="n">
-        <v>90983</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3741,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873644</v>
+        <v>873473</v>
       </c>
       <c r="R31" t="n">
-        <v>7392267</v>
+        <v>7392448</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3777,6 +3784,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3803,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123269191</v>
+        <v>123265693</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,37 +3831,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873680</v>
+        <v>873329</v>
       </c>
       <c r="R32" t="n">
-        <v>7392337</v>
+        <v>7392331</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3884,35 +3893,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269176</v>
+        <v>123265709</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,19 +3956,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873462</v>
+        <v>873407</v>
       </c>
       <c r="R33" t="n">
-        <v>7392294</v>
+        <v>7392275</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3996,29 +4006,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265704</v>
+        <v>123269168</v>
       </c>
       <c r="B34" t="n">
-        <v>79757</v>
+        <v>79885</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4031,34 +4040,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873421</v>
+        <v>873634</v>
       </c>
       <c r="R34" t="n">
-        <v>7392291</v>
+        <v>7392446</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4099,28 +4111,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265692</v>
+        <v>123265702</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4133,16 +4146,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4157,10 +4170,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873303</v>
+        <v>873647</v>
       </c>
       <c r="R35" t="n">
-        <v>7392314</v>
+        <v>7392305</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4197,7 +4210,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4224,10 +4237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269171</v>
+        <v>123269189</v>
       </c>
       <c r="B36" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873311</v>
+        <v>873683</v>
       </c>
       <c r="R36" t="n">
-        <v>7392309</v>
+        <v>7392341</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4303,11 +4316,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4335,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123269180</v>
+        <v>123265699</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>90977</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,41 +4355,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873544</v>
+        <v>873321</v>
       </c>
       <c r="R37" t="n">
-        <v>7392493</v>
+        <v>7392268</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4422,29 +4427,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269167</v>
+        <v>123265710</v>
       </c>
       <c r="B38" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,41 +4457,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873630</v>
+        <v>873472</v>
       </c>
       <c r="R38" t="n">
-        <v>7392455</v>
+        <v>7392425</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4528,29 +4529,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269178</v>
+        <v>123269174</v>
       </c>
       <c r="B39" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873536</v>
+        <v>873392</v>
       </c>
       <c r="R39" t="n">
-        <v>7392501</v>
+        <v>7392289</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269186</v>
+        <v>123269176</v>
       </c>
       <c r="B40" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873664</v>
+        <v>873462</v>
       </c>
       <c r="R40" t="n">
-        <v>7392361</v>
+        <v>7392294</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4752,14 +4752,14 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265702</v>
+        <v>123265701</v>
       </c>
       <c r="B41" t="n">
         <v>57497</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873647</v>
+        <v>873422</v>
       </c>
       <c r="R41" t="n">
-        <v>7392305</v>
+        <v>7392182</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Avbarkad tall, färska spår</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265711</v>
+        <v>123269186</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873476</v>
+        <v>873664</v>
       </c>
       <c r="R2" t="n">
-        <v>7392450</v>
+        <v>7392361</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269169</v>
+        <v>123269189</v>
       </c>
       <c r="B3" t="n">
-        <v>79760</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873659</v>
+        <v>873683</v>
       </c>
       <c r="R3" t="n">
-        <v>7392406</v>
+        <v>7392341</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123269165</v>
+        <v>123265716</v>
       </c>
       <c r="B4" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,41 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873352</v>
+        <v>873655</v>
       </c>
       <c r="R4" t="n">
-        <v>7392213</v>
+        <v>7392246</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -970,29 +971,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123269173</v>
+        <v>123265696</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>91003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,37 +1005,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873348</v>
+        <v>873644</v>
       </c>
       <c r="R5" t="n">
-        <v>7392214</v>
+        <v>7392267</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,29 +1073,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265716</v>
+        <v>123269172</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,16 +1125,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873655</v>
+        <v>873484</v>
       </c>
       <c r="R6" t="n">
-        <v>7392246</v>
+        <v>7392226</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1179,28 +1178,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265707</v>
+        <v>123265703</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>79766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,25 +1209,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873355</v>
+        <v>873327</v>
       </c>
       <c r="R7" t="n">
-        <v>7392213</v>
+        <v>7392254</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265698</v>
+        <v>123265702</v>
       </c>
       <c r="B8" t="n">
-        <v>79885</v>
+        <v>57503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873363</v>
+        <v>873647</v>
       </c>
       <c r="R8" t="n">
-        <v>7392320</v>
+        <v>7392305</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1375,6 +1375,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265705</v>
+        <v>123269191</v>
       </c>
       <c r="B9" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,34 +1422,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873470</v>
+        <v>873680</v>
       </c>
       <c r="R9" t="n">
-        <v>7392317</v>
+        <v>7392337</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1485,28 +1493,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269175</v>
+        <v>123269165</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,25 +1524,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873408</v>
+        <v>873352</v>
       </c>
       <c r="R10" t="n">
-        <v>7392282</v>
+        <v>7392213</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1612,7 +1621,7 @@
         <v>123265692</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265714</v>
+        <v>123265708</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873664</v>
+        <v>873329</v>
       </c>
       <c r="R12" t="n">
-        <v>7392383</v>
+        <v>7392332</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1818,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269172</v>
+        <v>123269173</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873484</v>
+        <v>873348</v>
       </c>
       <c r="R13" t="n">
-        <v>7392226</v>
+        <v>7392214</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1924,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269166</v>
+        <v>123269174</v>
       </c>
       <c r="B14" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1945,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873390</v>
+        <v>873392</v>
       </c>
       <c r="R14" t="n">
-        <v>7392303</v>
+        <v>7392289</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2030,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269182</v>
+        <v>123269168</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2051,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873578</v>
+        <v>873634</v>
       </c>
       <c r="R15" t="n">
-        <v>7392474</v>
+        <v>7392446</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2136,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265706</v>
+        <v>123265693</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2176,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873363</v>
+        <v>873329</v>
       </c>
       <c r="R16" t="n">
-        <v>7392216</v>
+        <v>7392331</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2216,7 +2225,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269188</v>
+        <v>123265704</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>79766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,41 +2264,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873662</v>
+        <v>873421</v>
       </c>
       <c r="R17" t="n">
-        <v>7392354</v>
+        <v>7392291</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2330,29 +2336,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269191</v>
+        <v>123265705</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,37 +2370,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873680</v>
+        <v>873470</v>
       </c>
       <c r="R18" t="n">
-        <v>7392337</v>
+        <v>7392317</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2436,29 +2438,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123265708</v>
+        <v>123269182</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,16 +2490,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873329</v>
+        <v>873578</v>
       </c>
       <c r="R19" t="n">
-        <v>7392332</v>
+        <v>7392474</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2539,28 +2543,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269167</v>
+        <v>123265698</v>
       </c>
       <c r="B20" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,19 +2596,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873630</v>
+        <v>873363</v>
       </c>
       <c r="R20" t="n">
-        <v>7392455</v>
+        <v>7392320</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2644,29 +2646,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269178</v>
+        <v>123269175</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873536</v>
+        <v>873408</v>
       </c>
       <c r="R21" t="n">
-        <v>7392501</v>
+        <v>7392282</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2769,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123265700</v>
+        <v>123269176</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,38 +2782,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873556</v>
+        <v>873462</v>
       </c>
       <c r="R22" t="n">
-        <v>7392510</v>
+        <v>7392294</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2853,28 +2857,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269171</v>
+        <v>123265710</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2905,19 +2910,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873311</v>
+        <v>873472</v>
       </c>
       <c r="R23" t="n">
-        <v>7392309</v>
+        <v>7392425</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2952,40 +2954,34 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269193</v>
+        <v>123265700</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>90994</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,41 +2990,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873639</v>
+        <v>873556</v>
       </c>
       <c r="R24" t="n">
-        <v>7392268</v>
+        <v>7392510</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,29 +3062,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123269186</v>
+        <v>123269167</v>
       </c>
       <c r="B25" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3100,25 +3092,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3123,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873664</v>
+        <v>873630</v>
       </c>
       <c r="R25" t="n">
-        <v>7392361</v>
+        <v>7392455</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3194,10 +3186,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265715</v>
+        <v>123265709</v>
       </c>
       <c r="B26" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,10 +3226,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873635</v>
+        <v>873407</v>
       </c>
       <c r="R26" t="n">
-        <v>7392257</v>
+        <v>7392275</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3296,10 +3288,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265704</v>
+        <v>123265715</v>
       </c>
       <c r="B27" t="n">
-        <v>79760</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3308,25 +3300,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3328,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873421</v>
+        <v>873635</v>
       </c>
       <c r="R27" t="n">
-        <v>7392291</v>
+        <v>7392257</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3398,10 +3390,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265696</v>
+        <v>123265713</v>
       </c>
       <c r="B28" t="n">
-        <v>90986</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3430,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873644</v>
+        <v>873664</v>
       </c>
       <c r="R28" t="n">
-        <v>7392267</v>
+        <v>7392383</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3500,10 +3492,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265703</v>
+        <v>123265706</v>
       </c>
       <c r="B29" t="n">
-        <v>79760</v>
+        <v>78781</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3512,25 +3504,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3540,10 +3532,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R29" t="n">
-        <v>7392254</v>
+        <v>7392216</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3576,6 +3568,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,10 +3599,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269180</v>
+        <v>123269193</v>
       </c>
       <c r="B30" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873544</v>
+        <v>873639</v>
       </c>
       <c r="R30" t="n">
-        <v>7392493</v>
+        <v>7392268</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3708,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265694</v>
+        <v>123269166</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,38 +3717,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873473</v>
+        <v>873390</v>
       </c>
       <c r="R31" t="n">
-        <v>7392448</v>
+        <v>7392303</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3786,39 +3786,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265693</v>
+        <v>123265711</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,21 +3827,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3855,10 +3851,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873329</v>
+        <v>873476</v>
       </c>
       <c r="R32" t="n">
-        <v>7392331</v>
+        <v>7392450</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3891,11 +3887,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3922,10 +3913,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265709</v>
+        <v>123269188</v>
       </c>
       <c r="B33" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,16 +3947,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873407</v>
+        <v>873662</v>
       </c>
       <c r="R33" t="n">
-        <v>7392275</v>
+        <v>7392354</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4006,28 +4000,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265702</v>
+        <v>123265694</v>
       </c>
       <c r="B34" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,16 +4035,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4064,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873647</v>
+        <v>873473</v>
       </c>
       <c r="R34" t="n">
-        <v>7392305</v>
+        <v>7392448</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4104,7 +4099,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Avbarkad tall, färska spår</t>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,10 +4126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123269168</v>
+        <v>123269171</v>
       </c>
       <c r="B35" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4143,25 +4138,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873634</v>
+        <v>873311</v>
       </c>
       <c r="R35" t="n">
-        <v>7392446</v>
+        <v>7392309</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4210,6 +4205,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269189</v>
+        <v>123269180</v>
       </c>
       <c r="B36" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873683</v>
+        <v>873544</v>
       </c>
       <c r="R36" t="n">
-        <v>7392341</v>
+        <v>7392493</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265699</v>
+        <v>123265701</v>
       </c>
       <c r="B37" t="n">
-        <v>90977</v>
+        <v>57503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,25 +4355,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873321</v>
+        <v>873422</v>
       </c>
       <c r="R37" t="n">
-        <v>7392268</v>
+        <v>7392182</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4419,6 +4419,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4445,10 +4450,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265710</v>
+        <v>123269169</v>
       </c>
       <c r="B38" t="n">
-        <v>78775</v>
+        <v>79766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,38 +4462,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873472</v>
+        <v>873659</v>
       </c>
       <c r="R38" t="n">
-        <v>7392425</v>
+        <v>7392406</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4529,28 +4537,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269174</v>
+        <v>123265699</v>
       </c>
       <c r="B39" t="n">
-        <v>78775</v>
+        <v>90994</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,41 +4568,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873392</v>
+        <v>873321</v>
       </c>
       <c r="R39" t="n">
-        <v>7392289</v>
+        <v>7392268</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4634,29 +4640,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269176</v>
+        <v>123269178</v>
       </c>
       <c r="B40" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873462</v>
+        <v>873536</v>
       </c>
       <c r="R40" t="n">
-        <v>7392294</v>
+        <v>7392501</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4759,10 +4764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265701</v>
+        <v>123265707</v>
       </c>
       <c r="B41" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,21 +4780,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4799,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873422</v>
+        <v>873355</v>
       </c>
       <c r="R41" t="n">
-        <v>7392182</v>
+        <v>7392213</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4835,11 +4840,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -2978,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265700</v>
+        <v>123269167</v>
       </c>
       <c r="B24" t="n">
-        <v>90994</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,34 +2994,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873556</v>
+        <v>873630</v>
       </c>
       <c r="R24" t="n">
-        <v>7392510</v>
+        <v>7392455</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,28 +3065,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123269167</v>
+        <v>123265700</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>90994</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3096,37 +3100,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873630</v>
+        <v>873556</v>
       </c>
       <c r="R25" t="n">
-        <v>7392455</v>
+        <v>7392510</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,19 +3168,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -2978,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269167</v>
+        <v>123265700</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>90994</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,37 +2994,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873630</v>
+        <v>873556</v>
       </c>
       <c r="R24" t="n">
-        <v>7392455</v>
+        <v>7392510</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3065,29 +3062,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265700</v>
+        <v>123269167</v>
       </c>
       <c r="B25" t="n">
-        <v>90994</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3100,34 +3096,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873556</v>
+        <v>873630</v>
       </c>
       <c r="R25" t="n">
-        <v>7392510</v>
+        <v>7392455</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3168,18 +3167,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -2978,10 +2978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265700</v>
+        <v>123269167</v>
       </c>
       <c r="B24" t="n">
-        <v>90994</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,34 +2994,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873556</v>
+        <v>873630</v>
       </c>
       <c r="R24" t="n">
-        <v>7392510</v>
+        <v>7392455</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,28 +3065,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123269167</v>
+        <v>123265700</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>90994</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3096,37 +3100,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873630</v>
+        <v>873556</v>
       </c>
       <c r="R25" t="n">
-        <v>7392455</v>
+        <v>7392510</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,19 +3168,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265694</v>
+        <v>123265699</v>
       </c>
       <c r="B34" t="n">
-        <v>57487</v>
+        <v>90994</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873473</v>
+        <v>873321</v>
       </c>
       <c r="R34" t="n">
-        <v>7392448</v>
+        <v>7392268</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4095,11 +4095,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4126,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123269171</v>
+        <v>123265694</v>
       </c>
       <c r="B35" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,37 +4137,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873311</v>
+        <v>873473</v>
       </c>
       <c r="R35" t="n">
-        <v>7392309</v>
+        <v>7392448</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4209,7 +4201,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4218,26 +4210,25 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269180</v>
+        <v>123269171</v>
       </c>
       <c r="B36" t="n">
         <v>78781</v>
@@ -4280,10 +4271,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873544</v>
+        <v>873311</v>
       </c>
       <c r="R36" t="n">
-        <v>7392493</v>
+        <v>7392309</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4316,6 +4307,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,10 +4339,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265701</v>
+        <v>123269180</v>
       </c>
       <c r="B37" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4359,34 +4355,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873422</v>
+        <v>873544</v>
       </c>
       <c r="R37" t="n">
-        <v>7392182</v>
+        <v>7392493</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4421,29 +4420,25 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4556,10 +4551,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265699</v>
+        <v>123265701</v>
       </c>
       <c r="B39" t="n">
-        <v>90994</v>
+        <v>57503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,25 +4563,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873321</v>
+        <v>873422</v>
       </c>
       <c r="R39" t="n">
-        <v>7392268</v>
+        <v>7392182</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4632,6 +4627,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269186</v>
+        <v>123269169</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R2" t="n">
-        <v>7392361</v>
+        <v>7392406</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269189</v>
+        <v>123265694</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873683</v>
+        <v>873473</v>
       </c>
       <c r="R3" t="n">
-        <v>7392341</v>
+        <v>7392448</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,35 +859,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265716</v>
+        <v>123265713</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873655</v>
+        <v>873664</v>
       </c>
       <c r="R4" t="n">
-        <v>7392246</v>
+        <v>7392383</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -989,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265696</v>
+        <v>123265710</v>
       </c>
       <c r="B5" t="n">
-        <v>91003</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873644</v>
+        <v>873472</v>
       </c>
       <c r="R5" t="n">
-        <v>7392267</v>
+        <v>7392425</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123269172</v>
+        <v>123265696</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,37 +1108,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873484</v>
+        <v>873644</v>
       </c>
       <c r="R6" t="n">
-        <v>7392226</v>
+        <v>7392267</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1178,29 +1176,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265703</v>
+        <v>123265698</v>
       </c>
       <c r="B7" t="n">
-        <v>79766</v>
+        <v>79896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R7" t="n">
-        <v>7392254</v>
+        <v>7392320</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1299,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265702</v>
+        <v>123269174</v>
       </c>
       <c r="B8" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,34 +1312,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873647</v>
+        <v>873392</v>
       </c>
       <c r="R8" t="n">
-        <v>7392305</v>
+        <v>7392289</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1377,39 +1377,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269191</v>
+        <v>123269180</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873680</v>
+        <v>873544</v>
       </c>
       <c r="R9" t="n">
-        <v>7392337</v>
+        <v>7392493</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1512,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269165</v>
+        <v>123269176</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,25 +1520,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873352</v>
+        <v>873462</v>
       </c>
       <c r="R10" t="n">
-        <v>7392213</v>
+        <v>7392294</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1618,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265692</v>
+        <v>123269166</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>79896</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,38 +1626,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873303</v>
+        <v>873390</v>
       </c>
       <c r="R11" t="n">
-        <v>7392314</v>
+        <v>7392303</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1696,39 +1695,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265708</v>
+        <v>123265709</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873329</v>
+        <v>873407</v>
       </c>
       <c r="R12" t="n">
-        <v>7392332</v>
+        <v>7392275</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269173</v>
+        <v>123265699</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>90999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,41 +1834,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873348</v>
+        <v>873321</v>
       </c>
       <c r="R13" t="n">
-        <v>7392214</v>
+        <v>7392268</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,29 +1906,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269174</v>
+        <v>123265715</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,19 +1958,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873392</v>
+        <v>873635</v>
       </c>
       <c r="R14" t="n">
-        <v>7392289</v>
+        <v>7392257</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2020,29 +2008,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269168</v>
+        <v>123265711</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,41 +2038,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873634</v>
+        <v>873476</v>
       </c>
       <c r="R15" t="n">
-        <v>7392446</v>
+        <v>7392450</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2126,29 +2110,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265693</v>
+        <v>123265701</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,16 +2144,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2185,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873329</v>
+        <v>873422</v>
       </c>
       <c r="R16" t="n">
-        <v>7392331</v>
+        <v>7392182</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,7 +2208,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2238,7 @@
         <v>123265704</v>
       </c>
       <c r="B17" t="n">
-        <v>79766</v>
+        <v>79771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265705</v>
+        <v>123269182</v>
       </c>
       <c r="B18" t="n">
-        <v>78517</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,34 +2353,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873470</v>
+        <v>873578</v>
       </c>
       <c r="R18" t="n">
-        <v>7392317</v>
+        <v>7392474</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2438,28 +2424,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269182</v>
+        <v>123269193</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873578</v>
+        <v>873639</v>
       </c>
       <c r="R19" t="n">
-        <v>7392474</v>
+        <v>7392268</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2562,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265698</v>
+        <v>123269188</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2574,38 +2561,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873363</v>
+        <v>873662</v>
       </c>
       <c r="R20" t="n">
-        <v>7392320</v>
+        <v>7392354</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2646,28 +2636,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269175</v>
+        <v>123269178</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873408</v>
+        <v>873536</v>
       </c>
       <c r="R21" t="n">
-        <v>7392282</v>
+        <v>7392501</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2770,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269176</v>
+        <v>123269189</v>
       </c>
       <c r="B22" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,10 +2804,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873462</v>
+        <v>873683</v>
       </c>
       <c r="R22" t="n">
-        <v>7392294</v>
+        <v>7392341</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2876,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123265710</v>
+        <v>123269167</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,38 +2879,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873472</v>
+        <v>873630</v>
       </c>
       <c r="R23" t="n">
-        <v>7392425</v>
+        <v>7392455</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2960,28 +2954,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269167</v>
+        <v>123269165</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>79896</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873630</v>
+        <v>873352</v>
       </c>
       <c r="R24" t="n">
-        <v>7392455</v>
+        <v>7392213</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3084,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265700</v>
+        <v>123265716</v>
       </c>
       <c r="B25" t="n">
-        <v>90994</v>
+        <v>78786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3096,25 +3091,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873556</v>
+        <v>873655</v>
       </c>
       <c r="R25" t="n">
-        <v>7392510</v>
+        <v>7392246</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3186,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265709</v>
+        <v>123269191</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,16 +3215,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873407</v>
+        <v>873680</v>
       </c>
       <c r="R26" t="n">
-        <v>7392275</v>
+        <v>7392337</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3270,28 +3268,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265715</v>
+        <v>123265706</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3328,10 +3327,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873635</v>
+        <v>873363</v>
       </c>
       <c r="R27" t="n">
-        <v>7392257</v>
+        <v>7392216</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3364,6 +3363,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3390,10 +3394,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265713</v>
+        <v>123269186</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,6 +3428,9 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
@@ -3433,7 +3440,7 @@
         <v>873664</v>
       </c>
       <c r="R28" t="n">
-        <v>7392383</v>
+        <v>7392361</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3474,28 +3481,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265706</v>
+        <v>123265702</v>
       </c>
       <c r="B29" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3508,21 +3516,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3532,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873363</v>
+        <v>873647</v>
       </c>
       <c r="R29" t="n">
-        <v>7392216</v>
+        <v>7392305</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3572,7 +3580,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3599,10 +3607,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269193</v>
+        <v>123269171</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873639</v>
+        <v>873311</v>
       </c>
       <c r="R30" t="n">
-        <v>7392268</v>
+        <v>7392309</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3678,6 +3686,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3705,10 +3718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123269166</v>
+        <v>123265707</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,41 +3730,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873390</v>
+        <v>873355</v>
       </c>
       <c r="R31" t="n">
-        <v>7392303</v>
+        <v>7392213</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3792,29 +3802,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265711</v>
+        <v>123269172</v>
       </c>
       <c r="B32" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3845,16 +3854,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873476</v>
+        <v>873484</v>
       </c>
       <c r="R32" t="n">
-        <v>7392450</v>
+        <v>7392226</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3895,28 +3907,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269188</v>
+        <v>123265708</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3947,19 +3960,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873662</v>
+        <v>873329</v>
       </c>
       <c r="R33" t="n">
-        <v>7392354</v>
+        <v>7392332</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4000,29 +4010,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265699</v>
+        <v>123269173</v>
       </c>
       <c r="B34" t="n">
-        <v>90994</v>
+        <v>78786</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4031,38 +4040,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873321</v>
+        <v>873348</v>
       </c>
       <c r="R34" t="n">
-        <v>7392268</v>
+        <v>7392214</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4103,28 +4115,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265694</v>
+        <v>123265705</v>
       </c>
       <c r="B35" t="n">
-        <v>57487</v>
+        <v>78522</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4137,21 +4150,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4161,10 +4174,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873473</v>
+        <v>873470</v>
       </c>
       <c r="R35" t="n">
-        <v>7392448</v>
+        <v>7392317</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4197,11 +4210,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4228,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269171</v>
+        <v>123269168</v>
       </c>
       <c r="B36" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4240,25 +4248,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4271,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873311</v>
+        <v>873634</v>
       </c>
       <c r="R36" t="n">
-        <v>7392309</v>
+        <v>7392446</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4307,11 +4315,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4339,10 +4342,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123269180</v>
+        <v>123265692</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,37 +4358,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873544</v>
+        <v>873303</v>
       </c>
       <c r="R37" t="n">
-        <v>7392493</v>
+        <v>7392314</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4420,35 +4420,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269169</v>
+        <v>123265693</v>
       </c>
       <c r="B38" t="n">
-        <v>79766</v>
+        <v>57490</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,41 +4461,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873659</v>
+        <v>873329</v>
       </c>
       <c r="R38" t="n">
-        <v>7392406</v>
+        <v>7392331</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4526,35 +4527,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265701</v>
+        <v>123269175</v>
       </c>
       <c r="B39" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4567,34 +4572,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873422</v>
+        <v>873408</v>
       </c>
       <c r="R39" t="n">
-        <v>7392182</v>
+        <v>7392282</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4629,39 +4637,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269178</v>
+        <v>123265700</v>
       </c>
       <c r="B40" t="n">
-        <v>78781</v>
+        <v>90999</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4670,41 +4674,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873536</v>
+        <v>873556</v>
       </c>
       <c r="R40" t="n">
-        <v>7392501</v>
+        <v>7392510</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4745,29 +4746,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265707</v>
+        <v>123265703</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
+        <v>79771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,25 +4776,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873355</v>
+        <v>873327</v>
       </c>
       <c r="R41" t="n">
-        <v>7392213</v>
+        <v>7392254</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269169</v>
+        <v>123265714</v>
       </c>
       <c r="B2" t="n">
-        <v>79771</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873659</v>
+        <v>873664</v>
       </c>
       <c r="R2" t="n">
-        <v>7392406</v>
+        <v>7392383</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,29 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123265694</v>
+        <v>123265710</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873473</v>
+        <v>873472</v>
       </c>
       <c r="R3" t="n">
-        <v>7392448</v>
+        <v>7392425</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265713</v>
+        <v>123269169</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R4" t="n">
-        <v>7392383</v>
+        <v>7392406</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,28 +966,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265710</v>
+        <v>123265699</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>91001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873472</v>
+        <v>873321</v>
       </c>
       <c r="R5" t="n">
-        <v>7392425</v>
+        <v>7392268</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265696</v>
+        <v>123265716</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873644</v>
+        <v>873655</v>
       </c>
       <c r="R6" t="n">
-        <v>7392267</v>
+        <v>7392246</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1194,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265698</v>
+        <v>123265692</v>
       </c>
       <c r="B7" t="n">
-        <v>79896</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873363</v>
+        <v>873303</v>
       </c>
       <c r="R7" t="n">
-        <v>7392320</v>
+        <v>7392314</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1270,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269174</v>
+        <v>123269165</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873392</v>
+        <v>873352</v>
       </c>
       <c r="R8" t="n">
-        <v>7392289</v>
+        <v>7392213</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269180</v>
+        <v>123269167</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,25 +1414,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873544</v>
+        <v>873630</v>
       </c>
       <c r="R9" t="n">
-        <v>7392493</v>
+        <v>7392455</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269176</v>
+        <v>123269193</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873462</v>
+        <v>873639</v>
       </c>
       <c r="R10" t="n">
-        <v>7392294</v>
+        <v>7392268</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269166</v>
+        <v>123269189</v>
       </c>
       <c r="B11" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1626,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873390</v>
+        <v>873683</v>
       </c>
       <c r="R11" t="n">
-        <v>7392303</v>
+        <v>7392341</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265709</v>
+        <v>123265705</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873407</v>
+        <v>873470</v>
       </c>
       <c r="R12" t="n">
-        <v>7392275</v>
+        <v>7392317</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123265699</v>
+        <v>123269191</v>
       </c>
       <c r="B13" t="n">
-        <v>90999</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,38 +1834,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873321</v>
+        <v>873680</v>
       </c>
       <c r="R13" t="n">
-        <v>7392268</v>
+        <v>7392337</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1906,28 +1909,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265715</v>
+        <v>123265696</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>91010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873635</v>
+        <v>873644</v>
       </c>
       <c r="R14" t="n">
-        <v>7392257</v>
+        <v>7392267</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2026,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123265711</v>
+        <v>123269180</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,16 +2064,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873476</v>
+        <v>873544</v>
       </c>
       <c r="R15" t="n">
-        <v>7392450</v>
+        <v>7392493</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2110,28 +2117,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265701</v>
+        <v>123269176</v>
       </c>
       <c r="B16" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,34 +2152,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873422</v>
+        <v>873462</v>
       </c>
       <c r="R16" t="n">
-        <v>7392182</v>
+        <v>7392294</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2206,39 +2217,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265704</v>
+        <v>123265701</v>
       </c>
       <c r="B17" t="n">
-        <v>79771</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2254,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873421</v>
+        <v>873422</v>
       </c>
       <c r="R17" t="n">
-        <v>7392291</v>
+        <v>7392182</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2311,6 +2318,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269182</v>
+        <v>123265707</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,19 +2383,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873578</v>
+        <v>873355</v>
       </c>
       <c r="R18" t="n">
-        <v>7392474</v>
+        <v>7392213</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,29 +2433,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269193</v>
+        <v>123265693</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2459,37 +2467,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873639</v>
+        <v>873329</v>
       </c>
       <c r="R19" t="n">
-        <v>7392268</v>
+        <v>7392331</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2524,35 +2529,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269188</v>
+        <v>123269186</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873662</v>
+        <v>873664</v>
       </c>
       <c r="R20" t="n">
-        <v>7392354</v>
+        <v>7392361</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2655,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269178</v>
+        <v>123269175</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2698,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873536</v>
+        <v>873408</v>
       </c>
       <c r="R21" t="n">
-        <v>7392501</v>
+        <v>7392282</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2761,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269189</v>
+        <v>123265715</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2795,19 +2804,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873683</v>
+        <v>873635</v>
       </c>
       <c r="R22" t="n">
-        <v>7392341</v>
+        <v>7392257</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2848,29 +2854,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269167</v>
+        <v>123269171</v>
       </c>
       <c r="B23" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2884,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873630</v>
+        <v>873311</v>
       </c>
       <c r="R23" t="n">
-        <v>7392455</v>
+        <v>7392309</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2946,6 +2951,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2973,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269165</v>
+        <v>123265708</v>
       </c>
       <c r="B24" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,41 +2995,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873352</v>
+        <v>873329</v>
       </c>
       <c r="R24" t="n">
-        <v>7392213</v>
+        <v>7392332</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3060,29 +3067,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265716</v>
+        <v>123269166</v>
       </c>
       <c r="B25" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,38 +3097,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873655</v>
+        <v>873390</v>
       </c>
       <c r="R25" t="n">
-        <v>7392246</v>
+        <v>7392303</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3163,28 +3172,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269191</v>
+        <v>123269174</v>
       </c>
       <c r="B26" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3224,10 +3234,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873680</v>
+        <v>873392</v>
       </c>
       <c r="R26" t="n">
-        <v>7392337</v>
+        <v>7392289</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3287,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265706</v>
+        <v>123265703</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>79773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3299,25 +3309,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3327,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873363</v>
+        <v>873327</v>
       </c>
       <c r="R27" t="n">
-        <v>7392216</v>
+        <v>7392254</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3363,11 +3373,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3394,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269186</v>
+        <v>123269188</v>
       </c>
       <c r="B28" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3437,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873664</v>
+        <v>873662</v>
       </c>
       <c r="R28" t="n">
-        <v>7392361</v>
+        <v>7392354</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3500,10 +3505,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265702</v>
+        <v>123265709</v>
       </c>
       <c r="B29" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,21 +3521,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3540,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873647</v>
+        <v>873407</v>
       </c>
       <c r="R29" t="n">
-        <v>7392305</v>
+        <v>7392275</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3576,11 +3581,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3607,10 +3607,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269171</v>
+        <v>123269182</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873311</v>
+        <v>873578</v>
       </c>
       <c r="R30" t="n">
-        <v>7392309</v>
+        <v>7392474</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3686,11 +3686,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3718,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265707</v>
+        <v>123265694</v>
       </c>
       <c r="B31" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3734,21 +3729,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3758,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873355</v>
+        <v>873473</v>
       </c>
       <c r="R31" t="n">
-        <v>7392213</v>
+        <v>7392448</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3794,6 +3789,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,10 +3820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123269172</v>
+        <v>123269178</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873484</v>
+        <v>873536</v>
       </c>
       <c r="R32" t="n">
-        <v>7392226</v>
+        <v>7392501</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265708</v>
+        <v>123265700</v>
       </c>
       <c r="B33" t="n">
-        <v>78786</v>
+        <v>91001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873329</v>
+        <v>873556</v>
       </c>
       <c r="R33" t="n">
-        <v>7392332</v>
+        <v>7392510</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123269173</v>
+        <v>123265702</v>
       </c>
       <c r="B34" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4044,37 +4044,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873348</v>
+        <v>873647</v>
       </c>
       <c r="R34" t="n">
-        <v>7392214</v>
+        <v>7392305</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4109,35 +4106,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265705</v>
+        <v>123265711</v>
       </c>
       <c r="B35" t="n">
-        <v>78522</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4150,21 +4151,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4174,10 +4175,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873470</v>
+        <v>873476</v>
       </c>
       <c r="R35" t="n">
-        <v>7392317</v>
+        <v>7392450</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4239,7 +4240,7 @@
         <v>123269168</v>
       </c>
       <c r="B36" t="n">
-        <v>79896</v>
+        <v>79898</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265692</v>
+        <v>123265706</v>
       </c>
       <c r="B37" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4358,21 +4359,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4383,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873303</v>
+        <v>873363</v>
       </c>
       <c r="R37" t="n">
-        <v>7392314</v>
+        <v>7392216</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4422,7 +4423,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4449,10 +4450,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265693</v>
+        <v>123265704</v>
       </c>
       <c r="B38" t="n">
-        <v>57490</v>
+        <v>79773</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4461,25 +4462,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4489,10 +4490,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873329</v>
+        <v>873421</v>
       </c>
       <c r="R38" t="n">
-        <v>7392331</v>
+        <v>7392291</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4525,11 +4526,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4556,10 +4552,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269175</v>
+        <v>123269173</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4599,10 +4595,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873408</v>
+        <v>873348</v>
       </c>
       <c r="R39" t="n">
-        <v>7392282</v>
+        <v>7392214</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4662,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123265700</v>
+        <v>123269172</v>
       </c>
       <c r="B40" t="n">
-        <v>90999</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4674,38 +4670,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873556</v>
+        <v>873484</v>
       </c>
       <c r="R40" t="n">
-        <v>7392510</v>
+        <v>7392226</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4746,28 +4745,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265703</v>
+        <v>123265698</v>
       </c>
       <c r="B41" t="n">
-        <v>79771</v>
+        <v>79898</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R41" t="n">
-        <v>7392254</v>
+        <v>7392320</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -3926,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265700</v>
+        <v>123265702</v>
       </c>
       <c r="B33" t="n">
-        <v>91001</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873556</v>
+        <v>873647</v>
       </c>
       <c r="R33" t="n">
-        <v>7392510</v>
+        <v>7392305</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4002,6 +4002,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,10 +4033,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265702</v>
+        <v>123265700</v>
       </c>
       <c r="B34" t="n">
-        <v>57507</v>
+        <v>91001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,25 +4045,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873647</v>
+        <v>873556</v>
       </c>
       <c r="R34" t="n">
-        <v>7392305</v>
+        <v>7392510</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4104,11 +4109,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269174</v>
+        <v>123265703</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,41 +3203,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873392</v>
+        <v>873327</v>
       </c>
       <c r="R26" t="n">
-        <v>7392289</v>
+        <v>7392254</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3278,29 +3275,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265703</v>
+        <v>123269174</v>
       </c>
       <c r="B27" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,38 +3305,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873327</v>
+        <v>873392</v>
       </c>
       <c r="R27" t="n">
-        <v>7392254</v>
+        <v>7392289</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3381,18 +3380,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265702</v>
+        <v>123265700</v>
       </c>
       <c r="B33" t="n">
-        <v>57507</v>
+        <v>91001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873647</v>
+        <v>873556</v>
       </c>
       <c r="R33" t="n">
-        <v>7392305</v>
+        <v>7392510</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4002,11 +4002,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4033,10 +4028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265700</v>
+        <v>123265702</v>
       </c>
       <c r="B34" t="n">
-        <v>91001</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,25 +4040,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873556</v>
+        <v>873647</v>
       </c>
       <c r="R34" t="n">
-        <v>7392510</v>
+        <v>7392305</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4109,6 +4104,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265714</v>
+        <v>123265699</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>91001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873664</v>
+        <v>873321</v>
       </c>
       <c r="R2" t="n">
-        <v>7392383</v>
+        <v>7392268</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123265710</v>
+        <v>123269186</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -811,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873472</v>
+        <v>873664</v>
       </c>
       <c r="R3" t="n">
-        <v>7392425</v>
+        <v>7392361</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123269169</v>
+        <v>123265714</v>
       </c>
       <c r="B4" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873659</v>
+        <v>873664</v>
       </c>
       <c r="R4" t="n">
-        <v>7392406</v>
+        <v>7392383</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -966,29 +967,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265699</v>
+        <v>123269171</v>
       </c>
       <c r="B5" t="n">
-        <v>91001</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +997,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873321</v>
+        <v>873311</v>
       </c>
       <c r="R5" t="n">
-        <v>7392268</v>
+        <v>7392309</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1063,34 +1066,40 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265716</v>
+        <v>123265698</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1108,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873655</v>
+        <v>873363</v>
       </c>
       <c r="R6" t="n">
-        <v>7392246</v>
+        <v>7392320</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1189,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265692</v>
+        <v>123265710</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873303</v>
+        <v>873472</v>
       </c>
       <c r="R7" t="n">
-        <v>7392314</v>
+        <v>7392425</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1265,11 +1274,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269165</v>
+        <v>123269180</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1312,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873352</v>
+        <v>873544</v>
       </c>
       <c r="R8" t="n">
-        <v>7392213</v>
+        <v>7392493</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1402,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123269167</v>
+        <v>123265694</v>
       </c>
       <c r="B9" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,41 +1418,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873630</v>
+        <v>873473</v>
       </c>
       <c r="R9" t="n">
-        <v>7392455</v>
+        <v>7392448</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1483,32 +1484,36 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269193</v>
+        <v>123269178</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873639</v>
+        <v>873536</v>
       </c>
       <c r="R10" t="n">
-        <v>7392268</v>
+        <v>7392501</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1614,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269189</v>
+        <v>123269167</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1631,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873683</v>
+        <v>873630</v>
       </c>
       <c r="R11" t="n">
-        <v>7392341</v>
+        <v>7392455</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265705</v>
+        <v>123265706</v>
       </c>
       <c r="B12" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873470</v>
+        <v>873363</v>
       </c>
       <c r="R12" t="n">
-        <v>7392317</v>
+        <v>7392216</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1796,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269191</v>
+        <v>123265708</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1856,19 +1866,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873680</v>
+        <v>873329</v>
       </c>
       <c r="R13" t="n">
-        <v>7392337</v>
+        <v>7392332</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1909,29 +1916,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265696</v>
+        <v>123265707</v>
       </c>
       <c r="B14" t="n">
-        <v>91010</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873644</v>
+        <v>873355</v>
       </c>
       <c r="R14" t="n">
-        <v>7392267</v>
+        <v>7392213</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2030,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269180</v>
+        <v>123265716</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2064,19 +2070,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873544</v>
+        <v>873655</v>
       </c>
       <c r="R15" t="n">
-        <v>7392493</v>
+        <v>7392246</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2117,29 +2120,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269176</v>
+        <v>123265692</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,37 +2154,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873462</v>
+        <v>873303</v>
       </c>
       <c r="R16" t="n">
-        <v>7392294</v>
+        <v>7392314</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2217,35 +2216,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265701</v>
+        <v>123269191</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,34 +2261,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873422</v>
+        <v>873680</v>
       </c>
       <c r="R17" t="n">
-        <v>7392182</v>
+        <v>7392337</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,36 +2326,32 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265707</v>
+        <v>123265711</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2389,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873355</v>
+        <v>873476</v>
       </c>
       <c r="R18" t="n">
-        <v>7392213</v>
+        <v>7392450</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2451,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123265693</v>
+        <v>123269169</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>79773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2463,38 +2465,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873329</v>
+        <v>873659</v>
       </c>
       <c r="R19" t="n">
-        <v>7392331</v>
+        <v>7392406</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2529,39 +2534,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269186</v>
+        <v>123265704</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,41 +2571,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873664</v>
+        <v>873421</v>
       </c>
       <c r="R20" t="n">
-        <v>7392361</v>
+        <v>7392291</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2645,26 +2643,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269175</v>
+        <v>123269172</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2707,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873408</v>
+        <v>873484</v>
       </c>
       <c r="R21" t="n">
-        <v>7392282</v>
+        <v>7392226</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2770,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123265715</v>
+        <v>123265702</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2786,21 +2783,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2810,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873635</v>
+        <v>873647</v>
       </c>
       <c r="R22" t="n">
-        <v>7392257</v>
+        <v>7392305</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2846,6 +2843,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2872,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269171</v>
+        <v>123269168</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,25 +2886,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2915,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873311</v>
+        <v>873634</v>
       </c>
       <c r="R23" t="n">
-        <v>7392309</v>
+        <v>7392446</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2951,11 +2953,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2983,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265708</v>
+        <v>123269174</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3017,16 +3014,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873329</v>
+        <v>873392</v>
       </c>
       <c r="R24" t="n">
-        <v>7392332</v>
+        <v>7392289</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3067,28 +3067,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123269166</v>
+        <v>123265696</v>
       </c>
       <c r="B25" t="n">
-        <v>79898</v>
+        <v>91010</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,41 +3098,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873390</v>
+        <v>873644</v>
       </c>
       <c r="R25" t="n">
-        <v>7392303</v>
+        <v>7392267</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,29 +3170,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265703</v>
+        <v>123269182</v>
       </c>
       <c r="B26" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,38 +3200,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873327</v>
+        <v>873578</v>
       </c>
       <c r="R26" t="n">
-        <v>7392254</v>
+        <v>7392474</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3275,25 +3275,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123269174</v>
+        <v>123269189</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3336,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873392</v>
+        <v>873683</v>
       </c>
       <c r="R27" t="n">
-        <v>7392289</v>
+        <v>7392341</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3399,10 +3400,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269188</v>
+        <v>123265705</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,37 +3416,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873662</v>
+        <v>873470</v>
       </c>
       <c r="R28" t="n">
-        <v>7392354</v>
+        <v>7392317</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3486,29 +3484,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265709</v>
+        <v>123265701</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,21 +3518,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3545,10 +3542,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873407</v>
+        <v>873422</v>
       </c>
       <c r="R29" t="n">
-        <v>7392275</v>
+        <v>7392182</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3581,6 +3578,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3607,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269182</v>
+        <v>123269165</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3619,25 +3621,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3650,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873578</v>
+        <v>873352</v>
       </c>
       <c r="R30" t="n">
-        <v>7392474</v>
+        <v>7392213</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3713,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265694</v>
+        <v>123265700</v>
       </c>
       <c r="B31" t="n">
-        <v>57491</v>
+        <v>91001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3725,25 +3727,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3753,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873473</v>
+        <v>873556</v>
       </c>
       <c r="R31" t="n">
-        <v>7392448</v>
+        <v>7392510</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3789,11 +3791,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,7 +3817,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123269178</v>
+        <v>123269173</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3863,10 +3860,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873536</v>
+        <v>873348</v>
       </c>
       <c r="R32" t="n">
-        <v>7392501</v>
+        <v>7392214</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,10 +3923,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265700</v>
+        <v>123269176</v>
       </c>
       <c r="B33" t="n">
-        <v>91001</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,38 +3935,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873556</v>
+        <v>873462</v>
       </c>
       <c r="R33" t="n">
-        <v>7392510</v>
+        <v>7392294</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4010,28 +4010,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265702</v>
+        <v>123269166</v>
       </c>
       <c r="B34" t="n">
-        <v>57507</v>
+        <v>79898</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,38 +4041,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873647</v>
+        <v>873390</v>
       </c>
       <c r="R34" t="n">
-        <v>7392305</v>
+        <v>7392303</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4106,36 +4110,32 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265711</v>
+        <v>123265709</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873476</v>
+        <v>873407</v>
       </c>
       <c r="R35" t="n">
-        <v>7392450</v>
+        <v>7392275</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4237,10 +4237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269168</v>
+        <v>123269175</v>
       </c>
       <c r="B36" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,25 +4249,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873634</v>
+        <v>873408</v>
       </c>
       <c r="R36" t="n">
-        <v>7392446</v>
+        <v>7392282</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265706</v>
+        <v>123269188</v>
       </c>
       <c r="B37" t="n">
         <v>78788</v>
@@ -4377,16 +4377,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873363</v>
+        <v>873662</v>
       </c>
       <c r="R37" t="n">
-        <v>7392216</v>
+        <v>7392354</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4421,39 +4424,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265704</v>
+        <v>123265715</v>
       </c>
       <c r="B38" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4462,25 +4461,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4490,10 +4489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873421</v>
+        <v>873635</v>
       </c>
       <c r="R38" t="n">
-        <v>7392291</v>
+        <v>7392257</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4552,10 +4551,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269173</v>
+        <v>123265703</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4564,41 +4563,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873348</v>
+        <v>873327</v>
       </c>
       <c r="R39" t="n">
-        <v>7392214</v>
+        <v>7392254</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4639,26 +4635,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269172</v>
+        <v>123269193</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4701,10 +4696,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873484</v>
+        <v>873639</v>
       </c>
       <c r="R40" t="n">
-        <v>7392226</v>
+        <v>7392268</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4764,10 +4759,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265698</v>
+        <v>123265693</v>
       </c>
       <c r="B41" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,25 +4771,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4799,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873363</v>
+        <v>873329</v>
       </c>
       <c r="R41" t="n">
-        <v>7392320</v>
+        <v>7392331</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4840,6 +4835,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123265699</v>
+        <v>123269172</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873321</v>
+        <v>873484</v>
       </c>
       <c r="R2" t="n">
-        <v>7392268</v>
+        <v>7392226</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269186</v>
+        <v>123269169</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R3" t="n">
-        <v>7392361</v>
+        <v>7392406</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265714</v>
+        <v>123269188</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -917,16 +921,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873664</v>
+        <v>873662</v>
       </c>
       <c r="R4" t="n">
-        <v>7392383</v>
+        <v>7392354</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -967,28 +974,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123269171</v>
+        <v>123265694</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,37 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873311</v>
+        <v>873473</v>
       </c>
       <c r="R5" t="n">
-        <v>7392309</v>
+        <v>7392448</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1068,7 +1073,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,29 +1082,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265698</v>
+        <v>123265709</v>
       </c>
       <c r="B6" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873363</v>
+        <v>873407</v>
       </c>
       <c r="R6" t="n">
-        <v>7392320</v>
+        <v>7392275</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265710</v>
+        <v>123269176</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1232,16 +1236,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873472</v>
+        <v>873462</v>
       </c>
       <c r="R7" t="n">
-        <v>7392425</v>
+        <v>7392294</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1282,28 +1289,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269180</v>
+        <v>123269167</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873544</v>
+        <v>873630</v>
       </c>
       <c r="R8" t="n">
-        <v>7392493</v>
+        <v>7392455</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1406,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265694</v>
+        <v>123265705</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>78524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873473</v>
+        <v>873470</v>
       </c>
       <c r="R9" t="n">
-        <v>7392448</v>
+        <v>7392317</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1482,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269178</v>
+        <v>123265699</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>91001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,41 +1528,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873536</v>
+        <v>873321</v>
       </c>
       <c r="R10" t="n">
-        <v>7392501</v>
+        <v>7392268</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1600,29 +1600,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269167</v>
+        <v>123265711</v>
       </c>
       <c r="B11" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,41 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873630</v>
+        <v>873476</v>
       </c>
       <c r="R11" t="n">
-        <v>7392455</v>
+        <v>7392450</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1706,29 +1702,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265706</v>
+        <v>123269168</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,38 +1732,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873363</v>
+        <v>873634</v>
       </c>
       <c r="R12" t="n">
-        <v>7392216</v>
+        <v>7392446</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1803,36 +1801,32 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123265708</v>
+        <v>123269189</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1866,16 +1860,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873329</v>
+        <v>873683</v>
       </c>
       <c r="R13" t="n">
-        <v>7392332</v>
+        <v>7392341</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1916,25 +1913,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265707</v>
+        <v>123269178</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1968,16 +1966,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873355</v>
+        <v>873536</v>
       </c>
       <c r="R14" t="n">
-        <v>7392213</v>
+        <v>7392501</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2018,25 +2019,26 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123265716</v>
+        <v>123269186</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2070,16 +2072,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873655</v>
+        <v>873664</v>
       </c>
       <c r="R15" t="n">
-        <v>7392246</v>
+        <v>7392361</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2120,28 +2125,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265692</v>
+        <v>123265698</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,25 +2156,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873303</v>
+        <v>873363</v>
       </c>
       <c r="R16" t="n">
-        <v>7392314</v>
+        <v>7392320</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,11 +2220,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,7 +2246,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123269191</v>
+        <v>123265716</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2279,19 +2280,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873680</v>
+        <v>873655</v>
       </c>
       <c r="R17" t="n">
-        <v>7392337</v>
+        <v>7392246</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2332,26 +2330,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265711</v>
+        <v>123265710</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2391,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873476</v>
+        <v>873472</v>
       </c>
       <c r="R18" t="n">
-        <v>7392450</v>
+        <v>7392425</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2453,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269169</v>
+        <v>123269166</v>
       </c>
       <c r="B19" t="n">
-        <v>79773</v>
+        <v>79898</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873659</v>
+        <v>873390</v>
       </c>
       <c r="R19" t="n">
-        <v>7392406</v>
+        <v>7392303</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2559,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265704</v>
+        <v>123269193</v>
       </c>
       <c r="B20" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,38 +2568,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873421</v>
+        <v>873639</v>
       </c>
       <c r="R20" t="n">
-        <v>7392291</v>
+        <v>7392268</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,25 +2643,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269172</v>
+        <v>123269171</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2704,10 +2705,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873484</v>
+        <v>873311</v>
       </c>
       <c r="R21" t="n">
-        <v>7392226</v>
+        <v>7392309</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2740,6 +2741,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2767,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123265702</v>
+        <v>123269180</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,34 +2789,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873647</v>
+        <v>873544</v>
       </c>
       <c r="R22" t="n">
-        <v>7392305</v>
+        <v>7392493</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2845,39 +2854,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269168</v>
+        <v>123265700</v>
       </c>
       <c r="B23" t="n">
-        <v>79898</v>
+        <v>91001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,37 +2895,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873634</v>
+        <v>873556</v>
       </c>
       <c r="R23" t="n">
-        <v>7392446</v>
+        <v>7392510</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2961,29 +2963,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123269174</v>
+        <v>123265692</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,37 +2997,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873392</v>
+        <v>873303</v>
       </c>
       <c r="R24" t="n">
-        <v>7392289</v>
+        <v>7392314</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3061,35 +3059,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265696</v>
+        <v>123265703</v>
       </c>
       <c r="B25" t="n">
-        <v>91010</v>
+        <v>79773</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,25 +3100,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873644</v>
+        <v>873327</v>
       </c>
       <c r="R25" t="n">
-        <v>7392267</v>
+        <v>7392254</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3188,7 +3190,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123269182</v>
+        <v>123265715</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3222,19 +3224,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873578</v>
+        <v>873635</v>
       </c>
       <c r="R26" t="n">
-        <v>7392474</v>
+        <v>7392257</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3275,26 +3274,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123269189</v>
+        <v>123265707</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3328,19 +3326,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873683</v>
+        <v>873355</v>
       </c>
       <c r="R27" t="n">
-        <v>7392341</v>
+        <v>7392213</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3381,29 +3376,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123265705</v>
+        <v>123269182</v>
       </c>
       <c r="B28" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3416,34 +3410,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873470</v>
+        <v>873578</v>
       </c>
       <c r="R28" t="n">
-        <v>7392317</v>
+        <v>7392474</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3484,28 +3481,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265701</v>
+        <v>123269191</v>
       </c>
       <c r="B29" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3518,34 +3516,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873422</v>
+        <v>873680</v>
       </c>
       <c r="R29" t="n">
-        <v>7392182</v>
+        <v>7392337</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3580,39 +3581,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269165</v>
+        <v>123269175</v>
       </c>
       <c r="B30" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,25 +3618,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3652,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873352</v>
+        <v>873408</v>
       </c>
       <c r="R30" t="n">
-        <v>7392213</v>
+        <v>7392282</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3715,10 +3712,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265700</v>
+        <v>123265693</v>
       </c>
       <c r="B31" t="n">
-        <v>91001</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,25 +3724,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3755,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873556</v>
+        <v>873329</v>
       </c>
       <c r="R31" t="n">
-        <v>7392510</v>
+        <v>7392331</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3791,6 +3788,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3817,7 +3819,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123269173</v>
+        <v>123265714</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3851,19 +3853,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873348</v>
+        <v>873664</v>
       </c>
       <c r="R32" t="n">
-        <v>7392214</v>
+        <v>7392383</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3904,26 +3903,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269176</v>
+        <v>123269173</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -3966,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873462</v>
+        <v>873348</v>
       </c>
       <c r="R33" t="n">
-        <v>7392294</v>
+        <v>7392214</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4029,10 +4027,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123269166</v>
+        <v>123265706</v>
       </c>
       <c r="B34" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4041,41 +4039,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873390</v>
+        <v>873363</v>
       </c>
       <c r="R34" t="n">
-        <v>7392303</v>
+        <v>7392216</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4110,35 +4105,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265709</v>
+        <v>123265704</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4147,25 +4146,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4175,10 +4174,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873407</v>
+        <v>873421</v>
       </c>
       <c r="R35" t="n">
-        <v>7392275</v>
+        <v>7392291</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4237,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123269175</v>
+        <v>123265701</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4253,37 +4252,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873408</v>
+        <v>873422</v>
       </c>
       <c r="R36" t="n">
-        <v>7392282</v>
+        <v>7392182</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4318,35 +4314,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123269188</v>
+        <v>123265696</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>91010</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4359,37 +4359,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873662</v>
+        <v>873644</v>
       </c>
       <c r="R37" t="n">
-        <v>7392354</v>
+        <v>7392267</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4430,29 +4427,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123265715</v>
+        <v>123269165</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4461,38 +4457,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873635</v>
+        <v>873352</v>
       </c>
       <c r="R38" t="n">
-        <v>7392257</v>
+        <v>7392213</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4533,28 +4532,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265703</v>
+        <v>123265708</v>
       </c>
       <c r="B39" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4563,25 +4563,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873327</v>
+        <v>873329</v>
       </c>
       <c r="R39" t="n">
-        <v>7392254</v>
+        <v>7392332</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269193</v>
+        <v>123269174</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873639</v>
+        <v>873392</v>
       </c>
       <c r="R40" t="n">
-        <v>7392268</v>
+        <v>7392289</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4759,10 +4759,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265693</v>
+        <v>123265702</v>
       </c>
       <c r="B41" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873329</v>
+        <v>873647</v>
       </c>
       <c r="R41" t="n">
-        <v>7392331</v>
+        <v>7392305</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269172</v>
+        <v>123269174</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873484</v>
+        <v>873392</v>
       </c>
       <c r="R2" t="n">
-        <v>7392226</v>
+        <v>7392289</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123269169</v>
+        <v>123265704</v>
       </c>
       <c r="B3" t="n">
         <v>79773</v>
@@ -815,19 +815,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873659</v>
+        <v>873421</v>
       </c>
       <c r="R3" t="n">
-        <v>7392406</v>
+        <v>7392291</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -868,26 +865,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123269188</v>
+        <v>123265710</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -921,19 +917,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873662</v>
+        <v>873472</v>
       </c>
       <c r="R4" t="n">
-        <v>7392354</v>
+        <v>7392425</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,29 +967,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265694</v>
+        <v>123265716</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873473</v>
+        <v>873655</v>
       </c>
       <c r="R5" t="n">
-        <v>7392448</v>
+        <v>7392246</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1069,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265709</v>
+        <v>123265694</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873407</v>
+        <v>873473</v>
       </c>
       <c r="R6" t="n">
-        <v>7392275</v>
+        <v>7392448</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1176,6 +1163,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269176</v>
+        <v>123265714</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1236,19 +1228,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873462</v>
+        <v>873664</v>
       </c>
       <c r="R7" t="n">
-        <v>7392294</v>
+        <v>7392383</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1289,29 +1278,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123269167</v>
+        <v>123265693</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,41 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>873630</v>
+        <v>873329</v>
       </c>
       <c r="R8" t="n">
-        <v>7392455</v>
+        <v>7392331</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,35 +1374,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265705</v>
+        <v>123265698</v>
       </c>
       <c r="B9" t="n">
-        <v>78524</v>
+        <v>79898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873470</v>
+        <v>873363</v>
       </c>
       <c r="R9" t="n">
-        <v>7392317</v>
+        <v>7392320</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1516,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123265699</v>
+        <v>123269182</v>
       </c>
       <c r="B10" t="n">
-        <v>91001</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,38 +1517,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873321</v>
+        <v>873578</v>
       </c>
       <c r="R10" t="n">
-        <v>7392268</v>
+        <v>7392474</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1600,25 +1592,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265711</v>
+        <v>123269178</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1652,16 +1645,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873476</v>
+        <v>873536</v>
       </c>
       <c r="R11" t="n">
-        <v>7392450</v>
+        <v>7392501</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1702,28 +1698,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269168</v>
+        <v>123265699</v>
       </c>
       <c r="B12" t="n">
-        <v>79898</v>
+        <v>91001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,37 +1733,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873634</v>
+        <v>873321</v>
       </c>
       <c r="R12" t="n">
-        <v>7392446</v>
+        <v>7392268</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1807,26 +1801,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269189</v>
+        <v>123269176</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1869,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873683</v>
+        <v>873462</v>
       </c>
       <c r="R13" t="n">
-        <v>7392341</v>
+        <v>7392294</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1932,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269178</v>
+        <v>123269166</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,25 +1937,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873536</v>
+        <v>873390</v>
       </c>
       <c r="R14" t="n">
-        <v>7392501</v>
+        <v>7392303</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2038,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269186</v>
+        <v>123269169</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873664</v>
+        <v>873659</v>
       </c>
       <c r="R15" t="n">
-        <v>7392361</v>
+        <v>7392406</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2144,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265698</v>
+        <v>123265703</v>
       </c>
       <c r="B16" t="n">
-        <v>79898</v>
+        <v>79773</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873363</v>
+        <v>873327</v>
       </c>
       <c r="R16" t="n">
-        <v>7392320</v>
+        <v>7392254</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2246,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265716</v>
+        <v>123265701</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2286,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873655</v>
+        <v>873422</v>
       </c>
       <c r="R17" t="n">
-        <v>7392246</v>
+        <v>7392182</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,6 +2315,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,7 +2346,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265710</v>
+        <v>123269180</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2382,16 +2380,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873472</v>
+        <v>873544</v>
       </c>
       <c r="R18" t="n">
-        <v>7392425</v>
+        <v>7392493</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2432,28 +2433,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269166</v>
+        <v>123269193</v>
       </c>
       <c r="B19" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2462,25 +2464,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2493,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873390</v>
+        <v>873639</v>
       </c>
       <c r="R19" t="n">
-        <v>7392303</v>
+        <v>7392268</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2556,7 +2558,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269193</v>
+        <v>123269188</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2599,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873639</v>
+        <v>873662</v>
       </c>
       <c r="R20" t="n">
-        <v>7392268</v>
+        <v>7392354</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2773,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269180</v>
+        <v>123269172</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2816,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873544</v>
+        <v>873484</v>
       </c>
       <c r="R22" t="n">
-        <v>7392493</v>
+        <v>7392226</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2879,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123265700</v>
+        <v>123269186</v>
       </c>
       <c r="B23" t="n">
-        <v>91001</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2891,38 +2893,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873556</v>
+        <v>873664</v>
       </c>
       <c r="R23" t="n">
-        <v>7392510</v>
+        <v>7392361</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2963,28 +2968,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265692</v>
+        <v>123265715</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,21 +3003,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3021,10 +3027,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873303</v>
+        <v>873635</v>
       </c>
       <c r="R24" t="n">
-        <v>7392314</v>
+        <v>7392257</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3057,11 +3063,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265703</v>
+        <v>123265706</v>
       </c>
       <c r="B25" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3100,25 +3101,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3128,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873327</v>
+        <v>873363</v>
       </c>
       <c r="R25" t="n">
-        <v>7392254</v>
+        <v>7392216</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3164,6 +3165,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265715</v>
+        <v>123265692</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,21 +3212,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3230,10 +3236,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873635</v>
+        <v>873303</v>
       </c>
       <c r="R26" t="n">
-        <v>7392257</v>
+        <v>7392314</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3266,6 +3272,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,7 +3303,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123265707</v>
+        <v>123269191</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3326,16 +3337,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873355</v>
+        <v>873680</v>
       </c>
       <c r="R27" t="n">
-        <v>7392213</v>
+        <v>7392337</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3376,25 +3390,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269182</v>
+        <v>123269173</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3437,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873578</v>
+        <v>873348</v>
       </c>
       <c r="R28" t="n">
-        <v>7392474</v>
+        <v>7392214</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3500,7 +3515,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123269191</v>
+        <v>123265707</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3534,19 +3549,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873680</v>
+        <v>873355</v>
       </c>
       <c r="R29" t="n">
-        <v>7392337</v>
+        <v>7392213</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3587,29 +3599,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123269175</v>
+        <v>123265702</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3622,37 +3633,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873408</v>
+        <v>873647</v>
       </c>
       <c r="R30" t="n">
-        <v>7392282</v>
+        <v>7392305</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3687,35 +3695,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265693</v>
+        <v>123265709</v>
       </c>
       <c r="B31" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3728,21 +3740,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3764,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873329</v>
+        <v>873407</v>
       </c>
       <c r="R31" t="n">
-        <v>7392331</v>
+        <v>7392275</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3788,11 +3800,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,7 +3826,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265714</v>
+        <v>123265711</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3859,10 +3866,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873664</v>
+        <v>873476</v>
       </c>
       <c r="R32" t="n">
-        <v>7392383</v>
+        <v>7392450</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3921,7 +3928,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123269173</v>
+        <v>123265708</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -3955,19 +3962,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873348</v>
+        <v>873329</v>
       </c>
       <c r="R33" t="n">
-        <v>7392214</v>
+        <v>7392332</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4008,26 +4012,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123265706</v>
+        <v>123269189</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -4061,16 +4064,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873363</v>
+        <v>873683</v>
       </c>
       <c r="R34" t="n">
-        <v>7392216</v>
+        <v>7392341</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4105,39 +4111,35 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123265704</v>
+        <v>123269175</v>
       </c>
       <c r="B35" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4146,38 +4148,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873421</v>
+        <v>873408</v>
       </c>
       <c r="R35" t="n">
-        <v>7392291</v>
+        <v>7392282</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4218,28 +4223,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265701</v>
+        <v>123265705</v>
       </c>
       <c r="B36" t="n">
-        <v>57507</v>
+        <v>78524</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,21 +4258,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4276,10 +4282,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873422</v>
+        <v>873470</v>
       </c>
       <c r="R36" t="n">
-        <v>7392182</v>
+        <v>7392317</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4312,11 +4318,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,10 +4344,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265696</v>
+        <v>123265700</v>
       </c>
       <c r="B37" t="n">
-        <v>91010</v>
+        <v>91001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,25 +4356,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4384,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873644</v>
+        <v>873556</v>
       </c>
       <c r="R37" t="n">
-        <v>7392267</v>
+        <v>7392510</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4445,7 +4446,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269165</v>
+        <v>123269167</v>
       </c>
       <c r="B38" t="n">
         <v>79898</v>
@@ -4488,10 +4489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873352</v>
+        <v>873630</v>
       </c>
       <c r="R38" t="n">
-        <v>7392213</v>
+        <v>7392455</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4551,10 +4552,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123265708</v>
+        <v>123269168</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4563,38 +4564,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873329</v>
+        <v>873634</v>
       </c>
       <c r="R39" t="n">
-        <v>7392332</v>
+        <v>7392446</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4635,28 +4639,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269174</v>
+        <v>123269165</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4665,25 +4670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4696,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873392</v>
+        <v>873352</v>
       </c>
       <c r="R40" t="n">
-        <v>7392289</v>
+        <v>7392213</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4759,10 +4764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265702</v>
+        <v>123265696</v>
       </c>
       <c r="B41" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,21 +4780,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4799,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873647</v>
+        <v>873644</v>
       </c>
       <c r="R41" t="n">
-        <v>7392305</v>
+        <v>7392267</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4835,11 +4840,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123269174</v>
+        <v>123265699</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>873392</v>
+        <v>873321</v>
       </c>
       <c r="R2" t="n">
-        <v>7392289</v>
+        <v>7392268</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123265704</v>
+        <v>123265700</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>873421</v>
+        <v>873556</v>
       </c>
       <c r="R3" t="n">
-        <v>7392291</v>
+        <v>7392510</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123265710</v>
+        <v>123265695</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>873472</v>
+        <v>873463</v>
       </c>
       <c r="R4" t="n">
-        <v>7392425</v>
+        <v>7392162</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -985,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123265716</v>
+        <v>123265696</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>873655</v>
+        <v>873644</v>
       </c>
       <c r="R5" t="n">
-        <v>7392246</v>
+        <v>7392267</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1087,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123265694</v>
+        <v>123265706</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>873473</v>
+        <v>873363</v>
       </c>
       <c r="R6" t="n">
-        <v>7392448</v>
+        <v>7392216</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1167,7 +1138,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera bohål, några färska</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,19 +1165,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123265714</v>
+        <v>123265707</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1234,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>873664</v>
+        <v>873355</v>
       </c>
       <c r="R7" t="n">
-        <v>7392383</v>
+        <v>7392213</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1296,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123265693</v>
+        <v>123265708</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,7 +1300,7 @@
         <v>873329</v>
       </c>
       <c r="R8" t="n">
-        <v>7392331</v>
+        <v>7392332</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1372,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,37 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123265698</v>
+        <v>123265709</v>
       </c>
       <c r="B9" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>873363</v>
+        <v>873407</v>
       </c>
       <c r="R9" t="n">
-        <v>7392320</v>
+        <v>7392275</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1505,19 +1456,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269182</v>
+        <v>123265710</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1539,19 +1485,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>873578</v>
+        <v>873472</v>
       </c>
       <c r="R10" t="n">
-        <v>7392474</v>
+        <v>7392425</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1592,38 +1535,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269178</v>
+        <v>123265711</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1645,19 +1582,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>873536</v>
+        <v>873476</v>
       </c>
       <c r="R11" t="n">
-        <v>7392501</v>
+        <v>7392450</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1698,56 +1632,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123265699</v>
+        <v>123265712</v>
       </c>
       <c r="B12" t="n">
-        <v>91001</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>873321</v>
+        <v>873664</v>
       </c>
       <c r="R12" t="n">
-        <v>7392268</v>
+        <v>7392440</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1793,6 +1721,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fertil med apothecier</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,19 +1752,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269176</v>
+        <v>123265713</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1853,19 +1781,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>873462</v>
+        <v>873664</v>
       </c>
       <c r="R13" t="n">
-        <v>7392294</v>
+        <v>7392383</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1906,72 +1831,63 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269166</v>
+        <v>123265715</v>
       </c>
       <c r="B14" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>873390</v>
+        <v>873635</v>
       </c>
       <c r="R14" t="n">
-        <v>7392303</v>
+        <v>7392257</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2012,72 +1928,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269169</v>
+        <v>123265716</v>
       </c>
       <c r="B15" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>873659</v>
+        <v>873655</v>
       </c>
       <c r="R15" t="n">
-        <v>7392406</v>
+        <v>7392246</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,69 +2025,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123265703</v>
+        <v>123269170</v>
       </c>
       <c r="B16" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>873327</v>
+        <v>873695</v>
       </c>
       <c r="R16" t="n">
-        <v>7392254</v>
+        <v>7392311</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2221,68 +2125,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265701</v>
+        <v>123269171</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>873422</v>
+        <v>873311</v>
       </c>
       <c r="R17" t="n">
-        <v>7392182</v>
+        <v>7392309</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2319,7 +2222,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hackspår på gran</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2328,37 +2231,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269180</v>
+        <v>123269172</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2389,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>873544</v>
+        <v>873484</v>
       </c>
       <c r="R18" t="n">
-        <v>7392493</v>
+        <v>7392226</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,19 +2351,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269193</v>
+        <v>123269173</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2495,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>873639</v>
+        <v>873348</v>
       </c>
       <c r="R19" t="n">
-        <v>7392268</v>
+        <v>7392214</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2558,19 +2452,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123269188</v>
+        <v>123269174</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2601,10 +2490,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>873662</v>
+        <v>873392</v>
       </c>
       <c r="R20" t="n">
-        <v>7392354</v>
+        <v>7392289</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2664,19 +2553,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123269171</v>
+        <v>123269175</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2707,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>873311</v>
+        <v>873408</v>
       </c>
       <c r="R21" t="n">
-        <v>7392309</v>
+        <v>7392282</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2743,11 +2627,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,19 +2654,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123269172</v>
+        <v>123269176</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2818,10 +2692,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>873484</v>
+        <v>873462</v>
       </c>
       <c r="R22" t="n">
-        <v>7392226</v>
+        <v>7392294</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2881,19 +2755,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123269186</v>
+        <v>123269178</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2924,10 +2793,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>873664</v>
+        <v>873536</v>
       </c>
       <c r="R23" t="n">
-        <v>7392361</v>
+        <v>7392501</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2987,19 +2856,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123265715</v>
+        <v>123269180</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3021,16 +2885,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>873635</v>
+        <v>873544</v>
       </c>
       <c r="R24" t="n">
-        <v>7392257</v>
+        <v>7392493</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3071,37 +2938,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123265706</v>
+        <v>123269182</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3123,16 +2986,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>873363</v>
+        <v>873578</v>
       </c>
       <c r="R25" t="n">
-        <v>7392216</v>
+        <v>7392474</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,79 +3033,73 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123265692</v>
+        <v>123269184</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>873303</v>
+        <v>873648</v>
       </c>
       <c r="R26" t="n">
-        <v>7392314</v>
+        <v>7392446</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3274,48 +3134,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123269191</v>
+        <v>123269185</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3346,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>873680</v>
+        <v>873675</v>
       </c>
       <c r="R27" t="n">
-        <v>7392337</v>
+        <v>7392425</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3409,19 +3260,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123269173</v>
+        <v>123269186</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3452,10 +3298,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>873348</v>
+        <v>873664</v>
       </c>
       <c r="R28" t="n">
-        <v>7392214</v>
+        <v>7392361</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3515,19 +3361,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123265707</v>
+        <v>123269188</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3549,16 +3390,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>873355</v>
+        <v>873662</v>
       </c>
       <c r="R29" t="n">
-        <v>7392213</v>
+        <v>7392354</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3599,68 +3443,67 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123265702</v>
+        <v>123269189</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>873647</v>
+        <v>873683</v>
       </c>
       <c r="R30" t="n">
-        <v>7392305</v>
+        <v>7392341</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3695,48 +3538,39 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Avbarkad tall, färska spår</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123265709</v>
+        <v>123269191</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3758,16 +3592,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>873407</v>
+        <v>873680</v>
       </c>
       <c r="R31" t="n">
-        <v>7392275</v>
+        <v>7392337</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3808,37 +3645,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123265711</v>
+        <v>123269193</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3860,16 +3693,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>873476</v>
+        <v>873639</v>
       </c>
       <c r="R32" t="n">
-        <v>7392450</v>
+        <v>7392268</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3910,33 +3746,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123265708</v>
+        <v>123265705</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3944,21 +3776,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3968,10 +3800,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>873329</v>
+        <v>873470</v>
       </c>
       <c r="R33" t="n">
-        <v>7392332</v>
+        <v>7392317</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4030,53 +3862,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123269189</v>
+        <v>123265703</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>873683</v>
+        <v>873327</v>
       </c>
       <c r="R34" t="n">
-        <v>7392341</v>
+        <v>7392254</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4117,72 +3941,63 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123269175</v>
+        <v>123265704</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>873408</v>
+        <v>873421</v>
       </c>
       <c r="R35" t="n">
-        <v>7392282</v>
+        <v>7392291</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4223,69 +4038,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123265705</v>
+        <v>123269169</v>
       </c>
       <c r="B36" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>873470</v>
+        <v>873659</v>
       </c>
       <c r="R36" t="n">
-        <v>7392317</v>
+        <v>7392406</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4326,33 +4138,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123265700</v>
+        <v>123265697</v>
       </c>
       <c r="B37" t="n">
-        <v>91001</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4360,21 +4168,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4384,10 +4192,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>873556</v>
+        <v>873715</v>
       </c>
       <c r="R37" t="n">
-        <v>7392510</v>
+        <v>7392256</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4446,15 +4254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123269167</v>
+        <v>123265698</v>
       </c>
       <c r="B38" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4480,19 +4283,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>873630</v>
+        <v>873363</v>
       </c>
       <c r="R38" t="n">
-        <v>7392455</v>
+        <v>7392320</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4533,34 +4333,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123269168</v>
+        <v>123269165</v>
       </c>
       <c r="B39" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>873634</v>
+        <v>873352</v>
       </c>
       <c r="R39" t="n">
-        <v>7392446</v>
+        <v>7392213</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4658,15 +4452,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123269165</v>
+        <v>123269166</v>
       </c>
       <c r="B40" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,10 +4490,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>873352</v>
+        <v>873390</v>
       </c>
       <c r="R40" t="n">
-        <v>7392213</v>
+        <v>7392303</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4764,50 +4553,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123265696</v>
+        <v>123269167</v>
       </c>
       <c r="B41" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Paharova, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>873644</v>
+        <v>873630</v>
       </c>
       <c r="R41" t="n">
-        <v>7392267</v>
+        <v>7392455</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4848,21 +4635,837 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123269168</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>873634</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7392446</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123265701</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>873422</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7392182</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Marie Persson</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123265702</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>873647</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7392305</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Avbarkad tall, färska spår</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123265691</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>873567</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7392201</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123265692</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>873303</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7392314</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123265693</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>873329</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7392331</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123265694</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>873473</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7392448</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera bohål, några färska</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123265690</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Paharova, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>873685</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7392238</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9923-2025 artfynd.xlsx
+++ b/artfynd/A 9923-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265700</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265695</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265709</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265710</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265713</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265715</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265716</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269170</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269171</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2449,6 +2539,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269173</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269174</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2651,6 +2751,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269175</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2752,6 +2857,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269176</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2853,6 +2963,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269178</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2954,6 +3069,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269180</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3055,6 +3175,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269182</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3156,6 +3281,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269184</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3257,6 +3387,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269185</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3358,6 +3493,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269186</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3459,6 +3599,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269188</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3560,6 +3705,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269189</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3661,6 +3811,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269191</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3762,6 +3917,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269193</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3859,6 +4019,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265705</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3956,6 +4121,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265703</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4053,6 +4223,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265704</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4154,6 +4329,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269169</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4251,6 +4431,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265697</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4348,6 +4533,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265698</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4449,6 +4639,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269165</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4550,6 +4745,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269166</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4651,6 +4851,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269167</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4752,6 +4957,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269168</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4854,6 +5064,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265701</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4956,6 +5171,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265702</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5058,6 +5278,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265691</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5160,6 +5385,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265692</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5262,6 +5492,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265693</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5364,6 +5599,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265694</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5466,8 +5706,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>